--- a/grupos/4BEM - Estadisticos 20212.xlsx
+++ b/grupos/4BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -182,25 +182,25 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Torres Sánchez José Luis</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Torres Sánchez José Luis</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>NC</t>
@@ -966,10 +966,10 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>-1</v>
@@ -981,10 +981,10 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1029,10 +1029,10 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>-1</v>
@@ -1044,10 +1044,10 @@
         <v>10</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1055,7 +1055,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>-1</v>
@@ -1070,10 +1070,10 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1118,7 +1118,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>-1</v>
@@ -1133,10 +1133,10 @@
         <v>9</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1144,10 +1144,10 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>-1</v>
@@ -1159,10 +1159,10 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1207,10 +1207,10 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>-1</v>
@@ -1222,10 +1222,10 @@
         <v>6</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1233,7 +1233,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>-1</v>
@@ -1248,7 +1248,7 @@
         <v>6</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1296,7 +1296,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>-1</v>
@@ -1311,7 +1311,7 @@
         <v>6</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC7">
         <v>-1</v>
@@ -1322,10 +1322,10 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>-1</v>
@@ -1337,10 +1337,10 @@
         <v>6</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1385,10 +1385,10 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>-1</v>
@@ -1400,10 +1400,10 @@
         <v>6</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1411,7 +1411,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>-1</v>
@@ -1426,10 +1426,10 @@
         <v>6</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1474,7 +1474,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>-1</v>
@@ -1489,10 +1489,10 @@
         <v>6</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1500,7 +1500,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>-1</v>
@@ -1515,10 +1515,10 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1563,7 +1563,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>-1</v>
@@ -1578,10 +1578,10 @@
         <v>10</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC10">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1589,10 +1589,10 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>-1</v>
@@ -1604,10 +1604,10 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1652,10 +1652,10 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>-1</v>
@@ -1667,10 +1667,10 @@
         <v>10</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1678,10 +1678,10 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <v>-1</v>
@@ -1693,10 +1693,10 @@
         <v>10</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1741,10 +1741,10 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>-1</v>
@@ -1756,10 +1756,10 @@
         <v>10</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1767,7 +1767,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>-1</v>
@@ -1782,7 +1782,7 @@
         <v>-1</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1830,7 +1830,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>-1</v>
@@ -1845,7 +1845,7 @@
         <v>-1</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC13">
         <v>-1</v>
@@ -1856,10 +1856,10 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>-1</v>
@@ -1871,10 +1871,10 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1919,10 +1919,10 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>-1</v>
@@ -1934,10 +1934,10 @@
         <v>10</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC14">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1945,10 +1945,10 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <v>-1</v>
@@ -1960,10 +1960,10 @@
         <v>8</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -2008,10 +2008,10 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>-1</v>
@@ -2023,10 +2023,10 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2034,7 +2034,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C16">
         <v>-1</v>
@@ -2049,10 +2049,10 @@
         <v>6</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2097,7 +2097,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>-1</v>
@@ -2112,10 +2112,10 @@
         <v>6</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC16">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2123,10 +2123,10 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>-1</v>
@@ -2138,10 +2138,10 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2186,10 +2186,10 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>-1</v>
@@ -2201,10 +2201,10 @@
         <v>10</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2212,7 +2212,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C18">
         <v>-1</v>
@@ -2227,10 +2227,10 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2275,7 +2275,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>-1</v>
@@ -2290,10 +2290,10 @@
         <v>10</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2301,7 +2301,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>-1</v>
@@ -2316,7 +2316,7 @@
         <v>-1</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2364,7 +2364,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>-1</v>
@@ -2379,7 +2379,7 @@
         <v>-1</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC19">
         <v>-1</v>
@@ -2390,10 +2390,10 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>-1</v>
@@ -2405,10 +2405,10 @@
         <v>6</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2453,10 +2453,10 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>-1</v>
@@ -2468,10 +2468,10 @@
         <v>6</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2479,10 +2479,10 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>-1</v>
@@ -2494,10 +2494,10 @@
         <v>7</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2542,10 +2542,10 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>-1</v>
@@ -2557,10 +2557,10 @@
         <v>7</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2568,7 +2568,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>-1</v>
@@ -2583,10 +2583,10 @@
         <v>6</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2631,7 +2631,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>-1</v>
@@ -2646,10 +2646,10 @@
         <v>6</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC22">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2657,7 +2657,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>-1</v>
@@ -2672,10 +2672,10 @@
         <v>-1</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2720,7 +2720,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>-1</v>
@@ -2735,10 +2735,10 @@
         <v>-1</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC23">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2746,7 +2746,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>-1</v>
@@ -2761,10 +2761,10 @@
         <v>-1</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2809,7 +2809,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>-1</v>
@@ -2824,10 +2824,10 @@
         <v>-1</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2835,7 +2835,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>-1</v>
@@ -2850,7 +2850,7 @@
         <v>6</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2898,7 +2898,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>-1</v>
@@ -2913,7 +2913,7 @@
         <v>6</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC25">
         <v>-1</v>
@@ -2924,10 +2924,10 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D26">
         <v>-1</v>
@@ -2939,10 +2939,10 @@
         <v>-1</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2987,10 +2987,10 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>-1</v>
@@ -3002,10 +3002,10 @@
         <v>-1</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC26">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3013,10 +3013,10 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>-1</v>
@@ -3028,10 +3028,10 @@
         <v>9</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -3076,10 +3076,10 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>-1</v>
@@ -3091,10 +3091,10 @@
         <v>9</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC27">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3102,10 +3102,10 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D28">
         <v>-1</v>
@@ -3117,10 +3117,10 @@
         <v>6</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -3165,10 +3165,10 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>-1</v>
@@ -3180,10 +3180,10 @@
         <v>6</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC28">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3191,10 +3191,10 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D29">
         <v>-1</v>
@@ -3206,10 +3206,10 @@
         <v>10</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -3254,10 +3254,10 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>-1</v>
@@ -3269,10 +3269,10 @@
         <v>10</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC29">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3280,10 +3280,10 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>-1</v>
@@ -3295,10 +3295,10 @@
         <v>10</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3343,10 +3343,10 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>-1</v>
@@ -3358,10 +3358,10 @@
         <v>10</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC30">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3369,10 +3369,10 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>-1</v>
@@ -3384,10 +3384,10 @@
         <v>8</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3432,10 +3432,10 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>-1</v>
@@ -3447,10 +3447,10 @@
         <v>8</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC31">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3458,10 +3458,10 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>-1</v>
@@ -3473,10 +3473,10 @@
         <v>9</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3521,10 +3521,10 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>-1</v>
@@ -3536,10 +3536,10 @@
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC32">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3547,10 +3547,10 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D33">
         <v>-1</v>
@@ -3562,10 +3562,10 @@
         <v>6</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3610,10 +3610,10 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>-1</v>
@@ -3625,10 +3625,10 @@
         <v>6</v>
       </c>
       <c r="AB33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC33">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3636,10 +3636,10 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D34">
         <v>-1</v>
@@ -3651,10 +3651,10 @@
         <v>6</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3699,10 +3699,10 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>-1</v>
@@ -3714,10 +3714,10 @@
         <v>6</v>
       </c>
       <c r="AB34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC34">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3725,7 +3725,7 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C35">
         <v>-1</v>
@@ -3740,10 +3740,10 @@
         <v>8</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3788,7 +3788,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>-1</v>
@@ -3803,10 +3803,10 @@
         <v>8</v>
       </c>
       <c r="AB35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC35">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3862,7 +3862,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3900,27 +3900,30 @@
         <v>33</v>
       </c>
       <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>48.48</v>
+      </c>
+      <c r="G3">
+        <v>51.52</v>
+      </c>
+      <c r="H3">
+        <v>5.9</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>33</v>
-      </c>
-      <c r="J3">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3929,27 +3932,30 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>60.61</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>7.3</v>
+      </c>
       <c r="I4">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3958,22 +3964,25 @@
         <v>33</v>
       </c>
       <c r="D5">
+        <v>24</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>72.73</v>
+      </c>
+      <c r="G5">
+        <v>27.27</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="E5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>33</v>
-      </c>
-      <c r="J5">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3987,27 +3996,30 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
+      <c r="H6">
+        <v>7.9</v>
+      </c>
       <c r="I6">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -4016,30 +4028,30 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>72.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="G7">
-        <v>27.27</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
@@ -4048,25 +4060,25 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>87.88</v>
+      </c>
+      <c r="G8">
+        <v>12.12</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>84.84999999999999</v>
-      </c>
-      <c r="G8">
+      <c r="J8">
         <v>0</v>
-      </c>
-      <c r="H8">
-        <v>7.9</v>
-      </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8">
-        <v>15.15</v>
       </c>
     </row>
   </sheetData>
@@ -4076,7 +4088,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F171"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4120,7 +4132,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4140,284 +4152,284 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920039</v>
+        <v>20330051920040</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920039</v>
+        <v>20330051920042</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920039</v>
+        <v>20330051920042</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920040</v>
+        <v>20330051920042</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920040</v>
+        <v>20330051920043</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920040</v>
+        <v>20330051920044</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920040</v>
+        <v>20330051920045</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920040</v>
+        <v>20330051920045</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920042</v>
+        <v>20330051920046</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920042</v>
+        <v>20330051920046</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920042</v>
+        <v>20330051920048</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920042</v>
+        <v>20330051920050</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920042</v>
+        <v>20330051920051</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920043</v>
+        <v>20330051920365</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
         <v>54</v>
@@ -4425,99 +4437,99 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920043</v>
+        <v>20330051920052</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920043</v>
+        <v>20330051920052</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920043</v>
+        <v>20330051920053</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920043</v>
+        <v>20330051920055</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920044</v>
+        <v>20330051920055</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
         <v>54</v>
@@ -4525,99 +4537,99 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920044</v>
+        <v>20330051920055</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920044</v>
+        <v>20330051920055</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920044</v>
+        <v>20330051920056</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920044</v>
+        <v>20330051920056</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920045</v>
+        <v>20330051920057</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
         <v>54</v>
@@ -4625,39 +4637,39 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920045</v>
+        <v>20330051920095</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920045</v>
+        <v>20330051920096</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
         <v>56</v>
@@ -4665,59 +4677,59 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920045</v>
+        <v>20330051920096</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920045</v>
+        <v>20330051920097</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="E31" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920046</v>
+        <v>20330051920097</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E32" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32" t="s">
         <v>54</v>
@@ -4725,76 +4737,70 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920046</v>
+        <v>20330051920097</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920046</v>
+        <v>20330051920097</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920046</v>
+        <v>20330051920099</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F35" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920046</v>
+        <v>20330051920099</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="E36" t="s">
         <v>11</v>
@@ -4805,219 +4811,219 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920048</v>
+        <v>20330051920366</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
         <v>78</v>
       </c>
       <c r="D37" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E37" t="s">
         <v>6</v>
       </c>
       <c r="F37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920048</v>
+        <v>20330051920366</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C38" t="s">
         <v>78</v>
       </c>
       <c r="D38" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
       </c>
       <c r="F38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920048</v>
+        <v>20330051920366</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
         <v>78</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E39" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F39" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920048</v>
+        <v>20330051920367</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
         <v>78</v>
       </c>
       <c r="D40" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920048</v>
+        <v>20330051920367</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C41" t="s">
         <v>78</v>
       </c>
       <c r="D41" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E41" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F41" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920050</v>
+        <v>20330051920367</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D42" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="E42" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920050</v>
+        <v>20330051920100</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="E43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F43" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920050</v>
+        <v>20330051920100</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C44" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="D44" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="E44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920050</v>
+        <v>20330051920100</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="D45" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920050</v>
+        <v>20330051920101</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C46" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="D46" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="E46" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F46" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920051</v>
+        <v>20330051920102</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D47" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="E47" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F47" t="s">
         <v>54</v>
@@ -5025,99 +5031,99 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>20330051920051</v>
+        <v>20330051920102</v>
       </c>
       <c r="B48" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D48" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="E48" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>20330051920051</v>
+        <v>20330051920058</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D49" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="E49" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F49" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>20330051920051</v>
+        <v>20330051920104</v>
       </c>
       <c r="B50" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D50" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F50" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>20330051920051</v>
+        <v>20330051920105</v>
       </c>
       <c r="B51" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D51" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="E51" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F51" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>20330051920365</v>
+        <v>20330051920107</v>
       </c>
       <c r="B52" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D52" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E52" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F52" t="s">
         <v>54</v>
@@ -5125,2367 +5131,102 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>20330051920365</v>
+        <v>20330051920109</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D53" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E53" t="s">
         <v>7</v>
       </c>
       <c r="F53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>20330051920365</v>
+        <v>20330051920111</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D54" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E54" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F54" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>20330051920365</v>
+        <v>20330051920112</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C55" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D55" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F55" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>20330051920365</v>
+        <v>20330051920113</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D56" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E56" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F56" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>20330051920052</v>
+        <v>20330051920113</v>
       </c>
       <c r="B57" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C57" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D57" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="E57" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F57" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>20330051920052</v>
-      </c>
-      <c r="B58" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" t="s">
-        <v>104</v>
-      </c>
-      <c r="D58" t="s">
-        <v>127</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>20330051920052</v>
-      </c>
-      <c r="B59" t="s">
-        <v>76</v>
-      </c>
-      <c r="C59" t="s">
-        <v>104</v>
-      </c>
-      <c r="D59" t="s">
-        <v>127</v>
-      </c>
-      <c r="E59" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920052</v>
-      </c>
-      <c r="B60" t="s">
-        <v>76</v>
-      </c>
-      <c r="C60" t="s">
-        <v>104</v>
-      </c>
-      <c r="D60" t="s">
-        <v>127</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920052</v>
-      </c>
-      <c r="B61" t="s">
-        <v>76</v>
-      </c>
-      <c r="C61" t="s">
-        <v>104</v>
-      </c>
-      <c r="D61" t="s">
-        <v>127</v>
-      </c>
-      <c r="E61" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920053</v>
-      </c>
-      <c r="B62" t="s">
-        <v>77</v>
-      </c>
-      <c r="C62" t="s">
-        <v>105</v>
-      </c>
-      <c r="D62" t="s">
-        <v>128</v>
-      </c>
-      <c r="E62" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>20330051920053</v>
-      </c>
-      <c r="B63" t="s">
-        <v>77</v>
-      </c>
-      <c r="C63" t="s">
-        <v>105</v>
-      </c>
-      <c r="D63" t="s">
-        <v>128</v>
-      </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>20330051920053</v>
-      </c>
-      <c r="B64" t="s">
-        <v>77</v>
-      </c>
-      <c r="C64" t="s">
-        <v>105</v>
-      </c>
-      <c r="D64" t="s">
-        <v>128</v>
-      </c>
-      <c r="E64" t="s">
-        <v>5</v>
-      </c>
-      <c r="F64" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>20330051920053</v>
-      </c>
-      <c r="B65" t="s">
-        <v>77</v>
-      </c>
-      <c r="C65" t="s">
-        <v>105</v>
-      </c>
-      <c r="D65" t="s">
-        <v>128</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>20330051920053</v>
-      </c>
-      <c r="B66" t="s">
-        <v>77</v>
-      </c>
-      <c r="C66" t="s">
-        <v>105</v>
-      </c>
-      <c r="D66" t="s">
-        <v>128</v>
-      </c>
-      <c r="E66" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>20330051920055</v>
-      </c>
-      <c r="B67" t="s">
-        <v>78</v>
-      </c>
-      <c r="C67" t="s">
-        <v>76</v>
-      </c>
-      <c r="D67" t="s">
-        <v>129</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>20330051920055</v>
-      </c>
-      <c r="B68" t="s">
-        <v>78</v>
-      </c>
-      <c r="C68" t="s">
-        <v>76</v>
-      </c>
-      <c r="D68" t="s">
-        <v>129</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>20330051920055</v>
-      </c>
-      <c r="B69" t="s">
-        <v>78</v>
-      </c>
-      <c r="C69" t="s">
-        <v>76</v>
-      </c>
-      <c r="D69" t="s">
-        <v>129</v>
-      </c>
-      <c r="E69" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>20330051920055</v>
-      </c>
-      <c r="B70" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70" t="s">
-        <v>76</v>
-      </c>
-      <c r="D70" t="s">
-        <v>129</v>
-      </c>
-      <c r="E70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>20330051920055</v>
-      </c>
-      <c r="B71" t="s">
-        <v>78</v>
-      </c>
-      <c r="C71" t="s">
-        <v>76</v>
-      </c>
-      <c r="D71" t="s">
-        <v>129</v>
-      </c>
-      <c r="E71" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>20330051920055</v>
-      </c>
-      <c r="B72" t="s">
-        <v>78</v>
-      </c>
-      <c r="C72" t="s">
-        <v>76</v>
-      </c>
-      <c r="D72" t="s">
-        <v>129</v>
-      </c>
-      <c r="E72" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920056</v>
-      </c>
-      <c r="B73" t="s">
-        <v>79</v>
-      </c>
-      <c r="C73" t="s">
-        <v>106</v>
-      </c>
-      <c r="D73" t="s">
-        <v>130</v>
-      </c>
-      <c r="E73" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>20330051920056</v>
-      </c>
-      <c r="B74" t="s">
-        <v>79</v>
-      </c>
-      <c r="C74" t="s">
-        <v>106</v>
-      </c>
-      <c r="D74" t="s">
-        <v>130</v>
-      </c>
-      <c r="E74" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>20330051920056</v>
-      </c>
-      <c r="B75" t="s">
-        <v>79</v>
-      </c>
-      <c r="C75" t="s">
-        <v>106</v>
-      </c>
-      <c r="D75" t="s">
-        <v>130</v>
-      </c>
-      <c r="E75" t="s">
-        <v>5</v>
-      </c>
-      <c r="F75" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>20330051920056</v>
-      </c>
-      <c r="B76" t="s">
-        <v>79</v>
-      </c>
-      <c r="C76" t="s">
-        <v>106</v>
-      </c>
-      <c r="D76" t="s">
-        <v>130</v>
-      </c>
-      <c r="E76" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>20330051920056</v>
-      </c>
-      <c r="B77" t="s">
-        <v>79</v>
-      </c>
-      <c r="C77" t="s">
-        <v>106</v>
-      </c>
-      <c r="D77" t="s">
-        <v>130</v>
-      </c>
-      <c r="E77" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>20330051920057</v>
-      </c>
-      <c r="B78" t="s">
-        <v>78</v>
-      </c>
-      <c r="C78" t="s">
-        <v>107</v>
-      </c>
-      <c r="D78" t="s">
-        <v>131</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>20330051920057</v>
-      </c>
-      <c r="B79" t="s">
-        <v>78</v>
-      </c>
-      <c r="C79" t="s">
-        <v>107</v>
-      </c>
-      <c r="D79" t="s">
-        <v>131</v>
-      </c>
-      <c r="E79" t="s">
-        <v>7</v>
-      </c>
-      <c r="F79" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>20330051920057</v>
-      </c>
-      <c r="B80" t="s">
-        <v>78</v>
-      </c>
-      <c r="C80" t="s">
-        <v>107</v>
-      </c>
-      <c r="D80" t="s">
-        <v>131</v>
-      </c>
-      <c r="E80" t="s">
-        <v>5</v>
-      </c>
-      <c r="F80" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>20330051920057</v>
-      </c>
-      <c r="B81" t="s">
-        <v>78</v>
-      </c>
-      <c r="C81" t="s">
-        <v>107</v>
-      </c>
-      <c r="D81" t="s">
-        <v>131</v>
-      </c>
-      <c r="E81" t="s">
-        <v>10</v>
-      </c>
-      <c r="F81" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>20330051920057</v>
-      </c>
-      <c r="B82" t="s">
-        <v>78</v>
-      </c>
-      <c r="C82" t="s">
-        <v>107</v>
-      </c>
-      <c r="D82" t="s">
-        <v>131</v>
-      </c>
-      <c r="E82" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>20330051920095</v>
-      </c>
-      <c r="B83" t="s">
-        <v>80</v>
-      </c>
-      <c r="C83" t="s">
-        <v>79</v>
-      </c>
-      <c r="D83" t="s">
-        <v>132</v>
-      </c>
-      <c r="E83" t="s">
-        <v>6</v>
-      </c>
-      <c r="F83" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>20330051920095</v>
-      </c>
-      <c r="B84" t="s">
-        <v>80</v>
-      </c>
-      <c r="C84" t="s">
-        <v>79</v>
-      </c>
-      <c r="D84" t="s">
-        <v>132</v>
-      </c>
-      <c r="E84" t="s">
-        <v>7</v>
-      </c>
-      <c r="F84" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>20330051920095</v>
-      </c>
-      <c r="B85" t="s">
-        <v>80</v>
-      </c>
-      <c r="C85" t="s">
-        <v>79</v>
-      </c>
-      <c r="D85" t="s">
-        <v>132</v>
-      </c>
-      <c r="E85" t="s">
-        <v>5</v>
-      </c>
-      <c r="F85" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>20330051920095</v>
-      </c>
-      <c r="B86" t="s">
-        <v>80</v>
-      </c>
-      <c r="C86" t="s">
-        <v>79</v>
-      </c>
-      <c r="D86" t="s">
-        <v>132</v>
-      </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>20330051920095</v>
-      </c>
-      <c r="B87" t="s">
-        <v>80</v>
-      </c>
-      <c r="C87" t="s">
-        <v>79</v>
-      </c>
-      <c r="D87" t="s">
-        <v>132</v>
-      </c>
-      <c r="E87" t="s">
-        <v>11</v>
-      </c>
-      <c r="F87" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>20330051920096</v>
-      </c>
-      <c r="B88" t="s">
-        <v>81</v>
-      </c>
-      <c r="C88" t="s">
-        <v>108</v>
-      </c>
-      <c r="D88" t="s">
-        <v>133</v>
-      </c>
-      <c r="E88" t="s">
-        <v>6</v>
-      </c>
-      <c r="F88" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>20330051920096</v>
-      </c>
-      <c r="B89" t="s">
-        <v>81</v>
-      </c>
-      <c r="C89" t="s">
-        <v>108</v>
-      </c>
-      <c r="D89" t="s">
-        <v>133</v>
-      </c>
-      <c r="E89" t="s">
-        <v>7</v>
-      </c>
-      <c r="F89" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>20330051920096</v>
-      </c>
-      <c r="B90" t="s">
-        <v>81</v>
-      </c>
-      <c r="C90" t="s">
-        <v>108</v>
-      </c>
-      <c r="D90" t="s">
-        <v>133</v>
-      </c>
-      <c r="E90" t="s">
-        <v>5</v>
-      </c>
-      <c r="F90" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>20330051920096</v>
-      </c>
-      <c r="B91" t="s">
-        <v>81</v>
-      </c>
-      <c r="C91" t="s">
-        <v>108</v>
-      </c>
-      <c r="D91" t="s">
-        <v>133</v>
-      </c>
-      <c r="E91" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>20330051920096</v>
-      </c>
-      <c r="B92" t="s">
-        <v>81</v>
-      </c>
-      <c r="C92" t="s">
-        <v>108</v>
-      </c>
-      <c r="D92" t="s">
-        <v>133</v>
-      </c>
-      <c r="E92" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>20330051920097</v>
-      </c>
-      <c r="B93" t="s">
-        <v>82</v>
-      </c>
-      <c r="C93" t="s">
-        <v>109</v>
-      </c>
-      <c r="D93" t="s">
-        <v>134</v>
-      </c>
-      <c r="E93" t="s">
-        <v>6</v>
-      </c>
-      <c r="F93" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>20330051920097</v>
-      </c>
-      <c r="B94" t="s">
-        <v>82</v>
-      </c>
-      <c r="C94" t="s">
-        <v>109</v>
-      </c>
-      <c r="D94" t="s">
-        <v>134</v>
-      </c>
-      <c r="E94" t="s">
-        <v>7</v>
-      </c>
-      <c r="F94" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>20330051920097</v>
-      </c>
-      <c r="B95" t="s">
-        <v>82</v>
-      </c>
-      <c r="C95" t="s">
-        <v>109</v>
-      </c>
-      <c r="D95" t="s">
-        <v>134</v>
-      </c>
-      <c r="E95" t="s">
-        <v>5</v>
-      </c>
-      <c r="F95" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>20330051920097</v>
-      </c>
-      <c r="B96" t="s">
-        <v>82</v>
-      </c>
-      <c r="C96" t="s">
-        <v>109</v>
-      </c>
-      <c r="D96" t="s">
-        <v>134</v>
-      </c>
-      <c r="E96" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>20330051920097</v>
-      </c>
-      <c r="B97" t="s">
-        <v>82</v>
-      </c>
-      <c r="C97" t="s">
-        <v>109</v>
-      </c>
-      <c r="D97" t="s">
-        <v>134</v>
-      </c>
-      <c r="E97" t="s">
-        <v>11</v>
-      </c>
-      <c r="F97" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>20330051920097</v>
-      </c>
-      <c r="B98" t="s">
-        <v>82</v>
-      </c>
-      <c r="C98" t="s">
-        <v>109</v>
-      </c>
-      <c r="D98" t="s">
-        <v>134</v>
-      </c>
-      <c r="E98" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>20330051920099</v>
-      </c>
-      <c r="B99" t="s">
-        <v>83</v>
-      </c>
-      <c r="D99" t="s">
-        <v>135</v>
-      </c>
-      <c r="E99" t="s">
-        <v>6</v>
-      </c>
-      <c r="F99" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>20330051920099</v>
-      </c>
-      <c r="B100" t="s">
-        <v>83</v>
-      </c>
-      <c r="D100" t="s">
-        <v>135</v>
-      </c>
-      <c r="E100" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>20330051920099</v>
-      </c>
-      <c r="B101" t="s">
-        <v>83</v>
-      </c>
-      <c r="D101" t="s">
-        <v>135</v>
-      </c>
-      <c r="E101" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>20330051920099</v>
-      </c>
-      <c r="B102" t="s">
-        <v>83</v>
-      </c>
-      <c r="D102" t="s">
-        <v>135</v>
-      </c>
-      <c r="E102" t="s">
-        <v>10</v>
-      </c>
-      <c r="F102" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>20330051920099</v>
-      </c>
-      <c r="B103" t="s">
-        <v>83</v>
-      </c>
-      <c r="D103" t="s">
-        <v>135</v>
-      </c>
-      <c r="E103" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>20330051920366</v>
-      </c>
-      <c r="B104" t="s">
-        <v>84</v>
-      </c>
-      <c r="C104" t="s">
-        <v>78</v>
-      </c>
-      <c r="D104" t="s">
-        <v>136</v>
-      </c>
-      <c r="E104" t="s">
-        <v>6</v>
-      </c>
-      <c r="F104" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>20330051920366</v>
-      </c>
-      <c r="B105" t="s">
-        <v>84</v>
-      </c>
-      <c r="C105" t="s">
-        <v>78</v>
-      </c>
-      <c r="D105" t="s">
-        <v>136</v>
-      </c>
-      <c r="E105" t="s">
-        <v>7</v>
-      </c>
-      <c r="F105" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>20330051920366</v>
-      </c>
-      <c r="B106" t="s">
-        <v>84</v>
-      </c>
-      <c r="C106" t="s">
-        <v>78</v>
-      </c>
-      <c r="D106" t="s">
-        <v>136</v>
-      </c>
-      <c r="E106" t="s">
-        <v>5</v>
-      </c>
-      <c r="F106" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>20330051920366</v>
-      </c>
-      <c r="B107" t="s">
-        <v>84</v>
-      </c>
-      <c r="C107" t="s">
-        <v>78</v>
-      </c>
-      <c r="D107" t="s">
-        <v>136</v>
-      </c>
-      <c r="E107" t="s">
-        <v>10</v>
-      </c>
-      <c r="F107" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>20330051920366</v>
-      </c>
-      <c r="B108" t="s">
-        <v>84</v>
-      </c>
-      <c r="C108" t="s">
-        <v>78</v>
-      </c>
-      <c r="D108" t="s">
-        <v>136</v>
-      </c>
-      <c r="E108" t="s">
-        <v>11</v>
-      </c>
-      <c r="F108" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>20330051920366</v>
-      </c>
-      <c r="B109" t="s">
-        <v>84</v>
-      </c>
-      <c r="C109" t="s">
-        <v>78</v>
-      </c>
-      <c r="D109" t="s">
-        <v>136</v>
-      </c>
-      <c r="E109" t="s">
-        <v>9</v>
-      </c>
-      <c r="F109" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>20330051920367</v>
-      </c>
-      <c r="B110" t="s">
-        <v>84</v>
-      </c>
-      <c r="C110" t="s">
-        <v>78</v>
-      </c>
-      <c r="D110" t="s">
-        <v>137</v>
-      </c>
-      <c r="E110" t="s">
-        <v>6</v>
-      </c>
-      <c r="F110" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>20330051920367</v>
-      </c>
-      <c r="B111" t="s">
-        <v>84</v>
-      </c>
-      <c r="C111" t="s">
-        <v>78</v>
-      </c>
-      <c r="D111" t="s">
-        <v>137</v>
-      </c>
-      <c r="E111" t="s">
-        <v>7</v>
-      </c>
-      <c r="F111" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>20330051920367</v>
-      </c>
-      <c r="B112" t="s">
-        <v>84</v>
-      </c>
-      <c r="C112" t="s">
-        <v>78</v>
-      </c>
-      <c r="D112" t="s">
-        <v>137</v>
-      </c>
-      <c r="E112" t="s">
-        <v>5</v>
-      </c>
-      <c r="F112" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>20330051920367</v>
-      </c>
-      <c r="B113" t="s">
-        <v>84</v>
-      </c>
-      <c r="C113" t="s">
-        <v>78</v>
-      </c>
-      <c r="D113" t="s">
-        <v>137</v>
-      </c>
-      <c r="E113" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>20330051920367</v>
-      </c>
-      <c r="B114" t="s">
-        <v>84</v>
-      </c>
-      <c r="C114" t="s">
-        <v>78</v>
-      </c>
-      <c r="D114" t="s">
-        <v>137</v>
-      </c>
-      <c r="E114" t="s">
-        <v>11</v>
-      </c>
-      <c r="F114" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>20330051920367</v>
-      </c>
-      <c r="B115" t="s">
-        <v>84</v>
-      </c>
-      <c r="C115" t="s">
-        <v>78</v>
-      </c>
-      <c r="D115" t="s">
-        <v>137</v>
-      </c>
-      <c r="E115" t="s">
-        <v>9</v>
-      </c>
-      <c r="F115" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>20330051920100</v>
-      </c>
-      <c r="B116" t="s">
-        <v>85</v>
-      </c>
-      <c r="C116" t="s">
-        <v>110</v>
-      </c>
-      <c r="D116" t="s">
-        <v>138</v>
-      </c>
-      <c r="E116" t="s">
-        <v>6</v>
-      </c>
-      <c r="F116" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>20330051920100</v>
-      </c>
-      <c r="B117" t="s">
-        <v>85</v>
-      </c>
-      <c r="C117" t="s">
-        <v>110</v>
-      </c>
-      <c r="D117" t="s">
-        <v>138</v>
-      </c>
-      <c r="E117" t="s">
-        <v>7</v>
-      </c>
-      <c r="F117" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>20330051920100</v>
-      </c>
-      <c r="B118" t="s">
-        <v>85</v>
-      </c>
-      <c r="C118" t="s">
-        <v>110</v>
-      </c>
-      <c r="D118" t="s">
-        <v>138</v>
-      </c>
-      <c r="E118" t="s">
-        <v>5</v>
-      </c>
-      <c r="F118" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>20330051920100</v>
-      </c>
-      <c r="B119" t="s">
-        <v>85</v>
-      </c>
-      <c r="C119" t="s">
-        <v>110</v>
-      </c>
-      <c r="D119" t="s">
-        <v>138</v>
-      </c>
-      <c r="E119" t="s">
-        <v>10</v>
-      </c>
-      <c r="F119" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>20330051920100</v>
-      </c>
-      <c r="B120" t="s">
-        <v>85</v>
-      </c>
-      <c r="C120" t="s">
-        <v>110</v>
-      </c>
-      <c r="D120" t="s">
-        <v>138</v>
-      </c>
-      <c r="E120" t="s">
-        <v>11</v>
-      </c>
-      <c r="F120" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>20330051920101</v>
-      </c>
-      <c r="B121" t="s">
-        <v>86</v>
-      </c>
-      <c r="C121" t="s">
-        <v>111</v>
-      </c>
-      <c r="D121" t="s">
-        <v>139</v>
-      </c>
-      <c r="E121" t="s">
-        <v>6</v>
-      </c>
-      <c r="F121" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>20330051920101</v>
-      </c>
-      <c r="B122" t="s">
-        <v>86</v>
-      </c>
-      <c r="C122" t="s">
-        <v>111</v>
-      </c>
-      <c r="D122" t="s">
-        <v>139</v>
-      </c>
-      <c r="E122" t="s">
-        <v>7</v>
-      </c>
-      <c r="F122" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>20330051920101</v>
-      </c>
-      <c r="B123" t="s">
-        <v>86</v>
-      </c>
-      <c r="C123" t="s">
-        <v>111</v>
-      </c>
-      <c r="D123" t="s">
-        <v>139</v>
-      </c>
-      <c r="E123" t="s">
-        <v>5</v>
-      </c>
-      <c r="F123" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>20330051920101</v>
-      </c>
-      <c r="B124" t="s">
-        <v>86</v>
-      </c>
-      <c r="C124" t="s">
-        <v>111</v>
-      </c>
-      <c r="D124" t="s">
-        <v>139</v>
-      </c>
-      <c r="E124" t="s">
-        <v>10</v>
-      </c>
-      <c r="F124" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>20330051920101</v>
-      </c>
-      <c r="B125" t="s">
-        <v>86</v>
-      </c>
-      <c r="C125" t="s">
-        <v>111</v>
-      </c>
-      <c r="D125" t="s">
-        <v>139</v>
-      </c>
-      <c r="E125" t="s">
-        <v>11</v>
-      </c>
-      <c r="F125" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>20330051920102</v>
-      </c>
-      <c r="B126" t="s">
-        <v>87</v>
-      </c>
-      <c r="C126" t="s">
-        <v>112</v>
-      </c>
-      <c r="D126" t="s">
-        <v>140</v>
-      </c>
-      <c r="E126" t="s">
-        <v>6</v>
-      </c>
-      <c r="F126" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>20330051920102</v>
-      </c>
-      <c r="B127" t="s">
-        <v>87</v>
-      </c>
-      <c r="C127" t="s">
-        <v>112</v>
-      </c>
-      <c r="D127" t="s">
-        <v>140</v>
-      </c>
-      <c r="E127" t="s">
-        <v>7</v>
-      </c>
-      <c r="F127" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>20330051920102</v>
-      </c>
-      <c r="B128" t="s">
-        <v>87</v>
-      </c>
-      <c r="C128" t="s">
-        <v>112</v>
-      </c>
-      <c r="D128" t="s">
-        <v>140</v>
-      </c>
-      <c r="E128" t="s">
-        <v>5</v>
-      </c>
-      <c r="F128" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>20330051920102</v>
-      </c>
-      <c r="B129" t="s">
-        <v>87</v>
-      </c>
-      <c r="C129" t="s">
-        <v>112</v>
-      </c>
-      <c r="D129" t="s">
-        <v>140</v>
-      </c>
-      <c r="E129" t="s">
-        <v>10</v>
-      </c>
-      <c r="F129" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>20330051920102</v>
-      </c>
-      <c r="B130" t="s">
-        <v>87</v>
-      </c>
-      <c r="C130" t="s">
-        <v>112</v>
-      </c>
-      <c r="D130" t="s">
-        <v>140</v>
-      </c>
-      <c r="E130" t="s">
-        <v>11</v>
-      </c>
-      <c r="F130" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>20330051920102</v>
-      </c>
-      <c r="B131" t="s">
-        <v>87</v>
-      </c>
-      <c r="C131" t="s">
-        <v>112</v>
-      </c>
-      <c r="D131" t="s">
-        <v>140</v>
-      </c>
-      <c r="E131" t="s">
-        <v>9</v>
-      </c>
-      <c r="F131" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>20330051920058</v>
-      </c>
-      <c r="B132" t="s">
-        <v>88</v>
-      </c>
-      <c r="C132" t="s">
-        <v>113</v>
-      </c>
-      <c r="D132" t="s">
-        <v>141</v>
-      </c>
-      <c r="E132" t="s">
-        <v>6</v>
-      </c>
-      <c r="F132" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>20330051920058</v>
-      </c>
-      <c r="B133" t="s">
-        <v>88</v>
-      </c>
-      <c r="C133" t="s">
-        <v>113</v>
-      </c>
-      <c r="D133" t="s">
-        <v>141</v>
-      </c>
-      <c r="E133" t="s">
-        <v>7</v>
-      </c>
-      <c r="F133" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134">
-        <v>20330051920058</v>
-      </c>
-      <c r="B134" t="s">
-        <v>88</v>
-      </c>
-      <c r="C134" t="s">
-        <v>113</v>
-      </c>
-      <c r="D134" t="s">
-        <v>141</v>
-      </c>
-      <c r="E134" t="s">
-        <v>5</v>
-      </c>
-      <c r="F134" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135">
-        <v>20330051920058</v>
-      </c>
-      <c r="B135" t="s">
-        <v>88</v>
-      </c>
-      <c r="C135" t="s">
-        <v>113</v>
-      </c>
-      <c r="D135" t="s">
-        <v>141</v>
-      </c>
-      <c r="E135" t="s">
-        <v>10</v>
-      </c>
-      <c r="F135" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136">
-        <v>20330051920058</v>
-      </c>
-      <c r="B136" t="s">
-        <v>88</v>
-      </c>
-      <c r="C136" t="s">
-        <v>113</v>
-      </c>
-      <c r="D136" t="s">
-        <v>141</v>
-      </c>
-      <c r="E136" t="s">
-        <v>11</v>
-      </c>
-      <c r="F136" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137">
-        <v>20330051920104</v>
-      </c>
-      <c r="B137" t="s">
-        <v>88</v>
-      </c>
-      <c r="C137" t="s">
-        <v>105</v>
-      </c>
-      <c r="D137" t="s">
-        <v>142</v>
-      </c>
-      <c r="E137" t="s">
-        <v>6</v>
-      </c>
-      <c r="F137" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138">
-        <v>20330051920104</v>
-      </c>
-      <c r="B138" t="s">
-        <v>88</v>
-      </c>
-      <c r="C138" t="s">
-        <v>105</v>
-      </c>
-      <c r="D138" t="s">
-        <v>142</v>
-      </c>
-      <c r="E138" t="s">
-        <v>7</v>
-      </c>
-      <c r="F138" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139">
-        <v>20330051920104</v>
-      </c>
-      <c r="B139" t="s">
-        <v>88</v>
-      </c>
-      <c r="C139" t="s">
-        <v>105</v>
-      </c>
-      <c r="D139" t="s">
-        <v>142</v>
-      </c>
-      <c r="E139" t="s">
-        <v>5</v>
-      </c>
-      <c r="F139" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140">
-        <v>20330051920104</v>
-      </c>
-      <c r="B140" t="s">
-        <v>88</v>
-      </c>
-      <c r="C140" t="s">
-        <v>105</v>
-      </c>
-      <c r="D140" t="s">
-        <v>142</v>
-      </c>
-      <c r="E140" t="s">
-        <v>10</v>
-      </c>
-      <c r="F140" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141">
-        <v>20330051920104</v>
-      </c>
-      <c r="B141" t="s">
-        <v>88</v>
-      </c>
-      <c r="C141" t="s">
-        <v>105</v>
-      </c>
-      <c r="D141" t="s">
-        <v>142</v>
-      </c>
-      <c r="E141" t="s">
-        <v>11</v>
-      </c>
-      <c r="F141" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142">
-        <v>20330051920105</v>
-      </c>
-      <c r="B142" t="s">
-        <v>89</v>
-      </c>
-      <c r="C142" t="s">
-        <v>81</v>
-      </c>
-      <c r="D142" t="s">
-        <v>143</v>
-      </c>
-      <c r="E142" t="s">
-        <v>6</v>
-      </c>
-      <c r="F142" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143">
-        <v>20330051920105</v>
-      </c>
-      <c r="B143" t="s">
-        <v>89</v>
-      </c>
-      <c r="C143" t="s">
-        <v>81</v>
-      </c>
-      <c r="D143" t="s">
-        <v>143</v>
-      </c>
-      <c r="E143" t="s">
-        <v>7</v>
-      </c>
-      <c r="F143" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144">
-        <v>20330051920105</v>
-      </c>
-      <c r="B144" t="s">
-        <v>89</v>
-      </c>
-      <c r="C144" t="s">
-        <v>81</v>
-      </c>
-      <c r="D144" t="s">
-        <v>143</v>
-      </c>
-      <c r="E144" t="s">
-        <v>5</v>
-      </c>
-      <c r="F144" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145">
-        <v>20330051920105</v>
-      </c>
-      <c r="B145" t="s">
-        <v>89</v>
-      </c>
-      <c r="C145" t="s">
-        <v>81</v>
-      </c>
-      <c r="D145" t="s">
-        <v>143</v>
-      </c>
-      <c r="E145" t="s">
-        <v>10</v>
-      </c>
-      <c r="F145" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146">
-        <v>20330051920105</v>
-      </c>
-      <c r="B146" t="s">
-        <v>89</v>
-      </c>
-      <c r="C146" t="s">
-        <v>81</v>
-      </c>
-      <c r="D146" t="s">
-        <v>143</v>
-      </c>
-      <c r="E146" t="s">
-        <v>11</v>
-      </c>
-      <c r="F146" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147">
-        <v>20330051920107</v>
-      </c>
-      <c r="B147" t="s">
-        <v>90</v>
-      </c>
-      <c r="C147" t="s">
-        <v>90</v>
-      </c>
-      <c r="D147" t="s">
-        <v>144</v>
-      </c>
-      <c r="E147" t="s">
-        <v>6</v>
-      </c>
-      <c r="F147" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148">
-        <v>20330051920107</v>
-      </c>
-      <c r="B148" t="s">
-        <v>90</v>
-      </c>
-      <c r="C148" t="s">
-        <v>90</v>
-      </c>
-      <c r="D148" t="s">
-        <v>144</v>
-      </c>
-      <c r="E148" t="s">
-        <v>7</v>
-      </c>
-      <c r="F148" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149">
-        <v>20330051920107</v>
-      </c>
-      <c r="B149" t="s">
-        <v>90</v>
-      </c>
-      <c r="C149" t="s">
-        <v>90</v>
-      </c>
-      <c r="D149" t="s">
-        <v>144</v>
-      </c>
-      <c r="E149" t="s">
-        <v>5</v>
-      </c>
-      <c r="F149" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150">
-        <v>20330051920107</v>
-      </c>
-      <c r="B150" t="s">
-        <v>90</v>
-      </c>
-      <c r="C150" t="s">
-        <v>90</v>
-      </c>
-      <c r="D150" t="s">
-        <v>144</v>
-      </c>
-      <c r="E150" t="s">
-        <v>10</v>
-      </c>
-      <c r="F150" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151">
-        <v>20330051920107</v>
-      </c>
-      <c r="B151" t="s">
-        <v>90</v>
-      </c>
-      <c r="C151" t="s">
-        <v>90</v>
-      </c>
-      <c r="D151" t="s">
-        <v>144</v>
-      </c>
-      <c r="E151" t="s">
-        <v>11</v>
-      </c>
-      <c r="F151" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152">
-        <v>20330051920109</v>
-      </c>
-      <c r="B152" t="s">
-        <v>91</v>
-      </c>
-      <c r="C152" t="s">
-        <v>101</v>
-      </c>
-      <c r="D152" t="s">
-        <v>145</v>
-      </c>
-      <c r="E152" t="s">
-        <v>6</v>
-      </c>
-      <c r="F152" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153">
-        <v>20330051920109</v>
-      </c>
-      <c r="B153" t="s">
-        <v>91</v>
-      </c>
-      <c r="C153" t="s">
-        <v>101</v>
-      </c>
-      <c r="D153" t="s">
-        <v>145</v>
-      </c>
-      <c r="E153" t="s">
-        <v>7</v>
-      </c>
-      <c r="F153" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154">
-        <v>20330051920109</v>
-      </c>
-      <c r="B154" t="s">
-        <v>91</v>
-      </c>
-      <c r="C154" t="s">
-        <v>101</v>
-      </c>
-      <c r="D154" t="s">
-        <v>145</v>
-      </c>
-      <c r="E154" t="s">
-        <v>5</v>
-      </c>
-      <c r="F154" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155">
-        <v>20330051920109</v>
-      </c>
-      <c r="B155" t="s">
-        <v>91</v>
-      </c>
-      <c r="C155" t="s">
-        <v>101</v>
-      </c>
-      <c r="D155" t="s">
-        <v>145</v>
-      </c>
-      <c r="E155" t="s">
-        <v>10</v>
-      </c>
-      <c r="F155" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156">
-        <v>20330051920109</v>
-      </c>
-      <c r="B156" t="s">
-        <v>91</v>
-      </c>
-      <c r="C156" t="s">
-        <v>101</v>
-      </c>
-      <c r="D156" t="s">
-        <v>145</v>
-      </c>
-      <c r="E156" t="s">
-        <v>11</v>
-      </c>
-      <c r="F156" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157">
-        <v>20330051920111</v>
-      </c>
-      <c r="B157" t="s">
-        <v>92</v>
-      </c>
-      <c r="C157" t="s">
-        <v>114</v>
-      </c>
-      <c r="D157" t="s">
-        <v>146</v>
-      </c>
-      <c r="E157" t="s">
-        <v>6</v>
-      </c>
-      <c r="F157" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158">
-        <v>20330051920111</v>
-      </c>
-      <c r="B158" t="s">
-        <v>92</v>
-      </c>
-      <c r="C158" t="s">
-        <v>114</v>
-      </c>
-      <c r="D158" t="s">
-        <v>146</v>
-      </c>
-      <c r="E158" t="s">
-        <v>7</v>
-      </c>
-      <c r="F158" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159">
-        <v>20330051920111</v>
-      </c>
-      <c r="B159" t="s">
-        <v>92</v>
-      </c>
-      <c r="C159" t="s">
-        <v>114</v>
-      </c>
-      <c r="D159" t="s">
-        <v>146</v>
-      </c>
-      <c r="E159" t="s">
-        <v>5</v>
-      </c>
-      <c r="F159" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160">
-        <v>20330051920111</v>
-      </c>
-      <c r="B160" t="s">
-        <v>92</v>
-      </c>
-      <c r="C160" t="s">
-        <v>114</v>
-      </c>
-      <c r="D160" t="s">
-        <v>146</v>
-      </c>
-      <c r="E160" t="s">
-        <v>10</v>
-      </c>
-      <c r="F160" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161">
-        <v>20330051920111</v>
-      </c>
-      <c r="B161" t="s">
-        <v>92</v>
-      </c>
-      <c r="C161" t="s">
-        <v>114</v>
-      </c>
-      <c r="D161" t="s">
-        <v>146</v>
-      </c>
-      <c r="E161" t="s">
-        <v>11</v>
-      </c>
-      <c r="F161" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162">
-        <v>20330051920112</v>
-      </c>
-      <c r="B162" t="s">
-        <v>93</v>
-      </c>
-      <c r="C162" t="s">
-        <v>115</v>
-      </c>
-      <c r="D162" t="s">
-        <v>147</v>
-      </c>
-      <c r="E162" t="s">
-        <v>6</v>
-      </c>
-      <c r="F162" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163">
-        <v>20330051920112</v>
-      </c>
-      <c r="B163" t="s">
-        <v>93</v>
-      </c>
-      <c r="C163" t="s">
-        <v>115</v>
-      </c>
-      <c r="D163" t="s">
-        <v>147</v>
-      </c>
-      <c r="E163" t="s">
-        <v>7</v>
-      </c>
-      <c r="F163" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164">
-        <v>20330051920112</v>
-      </c>
-      <c r="B164" t="s">
-        <v>93</v>
-      </c>
-      <c r="C164" t="s">
-        <v>115</v>
-      </c>
-      <c r="D164" t="s">
-        <v>147</v>
-      </c>
-      <c r="E164" t="s">
-        <v>5</v>
-      </c>
-      <c r="F164" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165">
-        <v>20330051920112</v>
-      </c>
-      <c r="B165" t="s">
-        <v>93</v>
-      </c>
-      <c r="C165" t="s">
-        <v>115</v>
-      </c>
-      <c r="D165" t="s">
-        <v>147</v>
-      </c>
-      <c r="E165" t="s">
-        <v>10</v>
-      </c>
-      <c r="F165" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
-      <c r="A166">
-        <v>20330051920112</v>
-      </c>
-      <c r="B166" t="s">
-        <v>93</v>
-      </c>
-      <c r="C166" t="s">
-        <v>115</v>
-      </c>
-      <c r="D166" t="s">
-        <v>147</v>
-      </c>
-      <c r="E166" t="s">
-        <v>11</v>
-      </c>
-      <c r="F166" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167">
-        <v>20330051920113</v>
-      </c>
-      <c r="B167" t="s">
-        <v>94</v>
-      </c>
-      <c r="C167" t="s">
-        <v>116</v>
-      </c>
-      <c r="D167" t="s">
-        <v>148</v>
-      </c>
-      <c r="E167" t="s">
-        <v>6</v>
-      </c>
-      <c r="F167" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
-      <c r="A168">
-        <v>20330051920113</v>
-      </c>
-      <c r="B168" t="s">
-        <v>94</v>
-      </c>
-      <c r="C168" t="s">
-        <v>116</v>
-      </c>
-      <c r="D168" t="s">
-        <v>148</v>
-      </c>
-      <c r="E168" t="s">
-        <v>7</v>
-      </c>
-      <c r="F168" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="A169">
-        <v>20330051920113</v>
-      </c>
-      <c r="B169" t="s">
-        <v>94</v>
-      </c>
-      <c r="C169" t="s">
-        <v>116</v>
-      </c>
-      <c r="D169" t="s">
-        <v>148</v>
-      </c>
-      <c r="E169" t="s">
-        <v>5</v>
-      </c>
-      <c r="F169" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
-      <c r="A170">
-        <v>20330051920113</v>
-      </c>
-      <c r="B170" t="s">
-        <v>94</v>
-      </c>
-      <c r="C170" t="s">
-        <v>116</v>
-      </c>
-      <c r="D170" t="s">
-        <v>148</v>
-      </c>
-      <c r="E170" t="s">
-        <v>10</v>
-      </c>
-      <c r="F170" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="A171">
-        <v>20330051920113</v>
-      </c>
-      <c r="B171" t="s">
-        <v>94</v>
-      </c>
-      <c r="C171" t="s">
-        <v>116</v>
-      </c>
-      <c r="D171" t="s">
-        <v>148</v>
-      </c>
-      <c r="E171" t="s">
-        <v>11</v>
-      </c>
-      <c r="F171" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -7533,7 +5274,7 @@
         <v>129</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -7550,29 +5291,29 @@
         <v>134</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920366</v>
+        <v>20330051920042</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920367</v>
+        <v>20330051920366</v>
       </c>
       <c r="B5" t="s">
         <v>84</v>
@@ -7581,500 +5322,500 @@
         <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920102</v>
+        <v>20330051920367</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920039</v>
+        <v>20330051920100</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920040</v>
+        <v>20330051920039</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920042</v>
+        <v>20330051920045</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920043</v>
+        <v>20330051920046</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920044</v>
+        <v>20330051920052</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920045</v>
+        <v>20330051920056</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920046</v>
+        <v>20330051920096</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920048</v>
+        <v>20330051920099</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920050</v>
+        <v>20330051920102</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920051</v>
+        <v>20330051920113</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920365</v>
+        <v>20330051920040</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920052</v>
+        <v>20330051920043</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920053</v>
+        <v>20330051920044</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920056</v>
+        <v>20330051920048</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920057</v>
+        <v>20330051920050</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920095</v>
+        <v>20330051920051</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920096</v>
+        <v>20330051920365</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920099</v>
+        <v>20330051920053</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>77</v>
+      </c>
+      <c r="C24" t="s">
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920100</v>
+        <v>20330051920057</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920101</v>
+        <v>20330051920095</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920058</v>
+        <v>20330051920101</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920104</v>
+        <v>20330051920058</v>
       </c>
       <c r="B28" t="s">
         <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920105</v>
+        <v>20330051920104</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920107</v>
+        <v>20330051920105</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920109</v>
+        <v>20330051920107</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920111</v>
+        <v>20330051920109</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920112</v>
+        <v>20330051920111</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920113</v>
+        <v>20330051920112</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8084,7 +5825,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8114,6 +5855,736 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920040</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920040</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920045</v>
+      </c>
+      <c r="B4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920045</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920046</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920046</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920365</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920365</v>
+      </c>
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920052</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920052</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920056</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920056</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920099</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920099</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920101</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920101</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" t="s">
+        <v>139</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920107</v>
+      </c>
+      <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920107</v>
+      </c>
+      <c r="B19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920109</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>145</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920109</v>
+      </c>
+      <c r="B21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920112</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" t="s">
+        <v>147</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920112</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" t="s">
+        <v>147</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920043</v>
+      </c>
+      <c r="B24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920048</v>
+      </c>
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" t="s">
+        <v>124</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920050</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920051</v>
+      </c>
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>54</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920053</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920057</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920095</v>
+      </c>
+      <c r="B30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920058</v>
+      </c>
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>20330051920104</v>
+      </c>
+      <c r="B32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>20330051920105</v>
+      </c>
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" t="s">
+        <v>143</v>
+      </c>
+      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/4BEM - Estadisticos 20212.xlsx
+++ b/grupos/4BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -182,18 +182,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Torres Sánchez José Luis</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Torres Sánchez José Luis</t>
+    <t>Avila Coronado Julieta</t>
   </si>
   <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -218,12 +218,90 @@
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>ANASTACIO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>HIRAM FABIAN</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
     <t>AMADOR</t>
   </si>
   <si>
-    <t>ANASTACIO</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -233,9 +311,6 @@
     <t>CITALAN</t>
   </si>
   <si>
-    <t>CID</t>
-  </si>
-  <si>
     <t>COLOHUA</t>
   </si>
   <si>
@@ -248,15 +323,9 @@
     <t>DIAZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -266,24 +335,9 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -305,15 +359,9 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
     <t>PORRAS</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>GARCÍA</t>
   </si>
   <si>
@@ -323,18 +371,12 @@
     <t>ROMANOS</t>
   </si>
   <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -347,18 +389,9 @@
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
     <t>ROSETE</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>BELLO</t>
   </si>
   <si>
@@ -371,15 +404,9 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
     <t>FRANCISCO ALAN</t>
   </si>
   <si>
-    <t>HIRAM FABIAN</t>
-  </si>
-  <si>
     <t>RAUL</t>
   </si>
   <si>
@@ -389,9 +416,6 @@
     <t>MISAEL</t>
   </si>
   <si>
-    <t>JESUS</t>
-  </si>
-  <si>
     <t>DAVID</t>
   </si>
   <si>
@@ -401,15 +425,9 @@
     <t>BRUNO AZAEL</t>
   </si>
   <si>
-    <t>CESAR</t>
-  </si>
-  <si>
     <t>MARIA ASUNCION</t>
   </si>
   <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
     <t>ROBERTO</t>
   </si>
   <si>
@@ -422,25 +440,7 @@
     <t>ADRIAN</t>
   </si>
   <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
     <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
   </si>
   <si>
     <t>ZURIEL ARTURO</t>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -1035,7 +1035,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>8</v>
@@ -1058,7 +1058,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>-1</v>
@@ -1121,7 +1121,7 @@
         <v>6</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>-1</v>
@@ -1150,7 +1150,7 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -1213,7 +1213,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>9</v>
@@ -1236,7 +1236,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>-1</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>-1</v>
@@ -1328,7 +1328,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1391,7 +1391,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>5</v>
@@ -1414,7 +1414,7 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>-1</v>
@@ -1477,7 +1477,7 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>-1</v>
@@ -1503,10 +1503,10 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1566,10 +1566,10 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z10">
         <v>10</v>
@@ -1595,7 +1595,7 @@
         <v>6</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1658,7 +1658,7 @@
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z11">
         <v>10</v>
@@ -1684,7 +1684,7 @@
         <v>9</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -1747,7 +1747,7 @@
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z12">
         <v>10</v>
@@ -1770,7 +1770,7 @@
         <v>5</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>-1</v>
@@ -1833,7 +1833,7 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>-1</v>
@@ -1862,7 +1862,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>7</v>
@@ -1925,7 +1925,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>7</v>
@@ -1951,7 +1951,7 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -2014,7 +2014,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>5</v>
@@ -2037,7 +2037,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>-1</v>
@@ -2100,7 +2100,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>-1</v>
@@ -2129,7 +2129,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>8</v>
@@ -2192,7 +2192,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <v>8</v>
@@ -2215,10 +2215,10 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E18">
         <v>10</v>
@@ -2278,10 +2278,10 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z18">
         <v>10</v>
@@ -2304,7 +2304,7 @@
         <v>5</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>-1</v>
@@ -2367,7 +2367,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>-1</v>
@@ -2396,7 +2396,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -2459,7 +2459,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z20">
         <v>6</v>
@@ -2485,7 +2485,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -2548,7 +2548,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>10</v>
@@ -2571,10 +2571,10 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>9</v>
@@ -2634,10 +2634,10 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <v>9</v>
@@ -2660,7 +2660,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>-1</v>
@@ -2723,7 +2723,7 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>-1</v>
@@ -2749,7 +2749,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>-1</v>
@@ -2812,7 +2812,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>-1</v>
@@ -2838,7 +2838,7 @@
         <v>5</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>-1</v>
@@ -2901,7 +2901,7 @@
         <v>5</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y25">
         <v>-1</v>
@@ -2930,7 +2930,7 @@
         <v>8</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E26">
         <v>6</v>
@@ -2993,7 +2993,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z26">
         <v>6</v>
@@ -3019,7 +3019,7 @@
         <v>6</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E27">
         <v>7</v>
@@ -3082,7 +3082,7 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z27">
         <v>7</v>
@@ -3108,7 +3108,7 @@
         <v>8</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>6</v>
@@ -3171,7 +3171,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>6</v>
@@ -3197,7 +3197,7 @@
         <v>9</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E29">
         <v>10</v>
@@ -3260,7 +3260,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z29">
         <v>10</v>
@@ -3286,7 +3286,7 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E30">
         <v>10</v>
@@ -3349,7 +3349,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>10</v>
@@ -3375,7 +3375,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E31">
         <v>6</v>
@@ -3438,7 +3438,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z31">
         <v>6</v>
@@ -3464,7 +3464,7 @@
         <v>6</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -3527,7 +3527,7 @@
         <v>6</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z32">
         <v>6</v>
@@ -3553,7 +3553,7 @@
         <v>6</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E33">
         <v>5</v>
@@ -3616,7 +3616,7 @@
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z33">
         <v>5</v>
@@ -3642,7 +3642,7 @@
         <v>8</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -3705,7 +3705,7 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z34">
         <v>6</v>
@@ -3728,10 +3728,10 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E35">
         <v>9</v>
@@ -3791,10 +3791,10 @@
         <v>6</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z35">
         <v>9</v>
@@ -3862,7 +3862,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3871,27 +3871,30 @@
         <v>33</v>
       </c>
       <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>48.48</v>
+      </c>
+      <c r="G2">
+        <v>51.52</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>33</v>
-      </c>
-      <c r="J2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3900,30 +3903,30 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>48.48</v>
+        <v>69.7</v>
       </c>
       <c r="G3">
-        <v>51.52</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3932,30 +3935,30 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>72.73</v>
+      </c>
+      <c r="G4">
+        <v>27.27</v>
+      </c>
+      <c r="H4">
+        <v>7.1</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>60.61</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>7.3</v>
-      </c>
-      <c r="I4">
-        <v>13</v>
-      </c>
-      <c r="J4">
-        <v>39.39</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3964,19 +3967,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>72.73</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="G5">
-        <v>27.27</v>
+        <v>18.18</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4088,7 +4091,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4123,1110 +4126,390 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920039</v>
+        <v>20330051920042</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920040</v>
+        <v>20330051920042</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920042</v>
+        <v>20330051920046</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920042</v>
+        <v>20330051920052</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920042</v>
+        <v>20330051920055</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920043</v>
+        <v>20330051920055</v>
       </c>
       <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" t="s">
         <v>68</v>
       </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920044</v>
+        <v>20330051920055</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920045</v>
+        <v>20330051920097</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920045</v>
+        <v>20330051920097</v>
       </c>
       <c r="B11" t="s">
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920046</v>
+        <v>20330051920097</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920046</v>
+        <v>20330051920099</v>
       </c>
       <c r="B13" t="s">
         <v>71</v>
       </c>
-      <c r="C13" t="s">
-        <v>101</v>
-      </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920048</v>
+        <v>20330051920099</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920050</v>
+        <v>20330051920366</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920051</v>
+        <v>20330051920366</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920365</v>
+        <v>20330051920367</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920052</v>
+        <v>20330051920367</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920052</v>
+        <v>20330051920100</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920053</v>
+        <v>20330051920100</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920055</v>
+        <v>20330051920102</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920055</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920055</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" t="s">
-        <v>129</v>
-      </c>
-      <c r="E23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920055</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920056</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" t="s">
-        <v>130</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920056</v>
-      </c>
-      <c r="B26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" t="s">
-        <v>130</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920057</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" t="s">
-        <v>131</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920095</v>
-      </c>
-      <c r="B28" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" t="s">
-        <v>132</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920096</v>
-      </c>
-      <c r="B29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" t="s">
-        <v>133</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920096</v>
-      </c>
-      <c r="B30" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" t="s">
-        <v>108</v>
-      </c>
-      <c r="D30" t="s">
-        <v>133</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920097</v>
-      </c>
-      <c r="B31" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" t="s">
-        <v>134</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920097</v>
-      </c>
-      <c r="B32" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" t="s">
-        <v>109</v>
-      </c>
-      <c r="D32" t="s">
-        <v>134</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920097</v>
-      </c>
-      <c r="B33" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" t="s">
-        <v>109</v>
-      </c>
-      <c r="D33" t="s">
-        <v>134</v>
-      </c>
-      <c r="E33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920097</v>
-      </c>
-      <c r="B34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34" t="s">
-        <v>134</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920099</v>
-      </c>
-      <c r="B35" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" t="s">
-        <v>135</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920099</v>
-      </c>
-      <c r="B36" t="s">
-        <v>83</v>
-      </c>
-      <c r="D36" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920366</v>
-      </c>
-      <c r="B37" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" t="s">
-        <v>136</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920366</v>
-      </c>
-      <c r="B38" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" t="s">
-        <v>136</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920366</v>
-      </c>
-      <c r="B39" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" t="s">
-        <v>78</v>
-      </c>
-      <c r="D39" t="s">
-        <v>136</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920367</v>
-      </c>
-      <c r="B40" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" t="s">
-        <v>78</v>
-      </c>
-      <c r="D40" t="s">
-        <v>137</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920367</v>
-      </c>
-      <c r="B41" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" t="s">
-        <v>78</v>
-      </c>
-      <c r="D41" t="s">
-        <v>137</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920367</v>
-      </c>
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" t="s">
-        <v>137</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920100</v>
-      </c>
-      <c r="B43" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" t="s">
-        <v>110</v>
-      </c>
-      <c r="D43" t="s">
-        <v>138</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920100</v>
-      </c>
-      <c r="B44" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" t="s">
-        <v>110</v>
-      </c>
-      <c r="D44" t="s">
-        <v>138</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920100</v>
-      </c>
-      <c r="B45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C45" t="s">
-        <v>110</v>
-      </c>
-      <c r="D45" t="s">
-        <v>138</v>
-      </c>
-      <c r="E45" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920101</v>
-      </c>
-      <c r="B46" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46" t="s">
-        <v>111</v>
-      </c>
-      <c r="D46" t="s">
-        <v>139</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920102</v>
-      </c>
-      <c r="B47" t="s">
-        <v>87</v>
-      </c>
-      <c r="C47" t="s">
-        <v>112</v>
-      </c>
-      <c r="D47" t="s">
-        <v>140</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920102</v>
-      </c>
-      <c r="B48" t="s">
-        <v>87</v>
-      </c>
-      <c r="C48" t="s">
-        <v>112</v>
-      </c>
-      <c r="D48" t="s">
-        <v>140</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920058</v>
-      </c>
-      <c r="B49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" t="s">
-        <v>113</v>
-      </c>
-      <c r="D49" t="s">
-        <v>141</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920104</v>
-      </c>
-      <c r="B50" t="s">
-        <v>88</v>
-      </c>
-      <c r="C50" t="s">
-        <v>105</v>
-      </c>
-      <c r="D50" t="s">
-        <v>142</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920105</v>
-      </c>
-      <c r="B51" t="s">
-        <v>89</v>
-      </c>
-      <c r="C51" t="s">
-        <v>81</v>
-      </c>
-      <c r="D51" t="s">
-        <v>143</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920107</v>
-      </c>
-      <c r="B52" t="s">
-        <v>90</v>
-      </c>
-      <c r="C52" t="s">
-        <v>90</v>
-      </c>
-      <c r="D52" t="s">
-        <v>144</v>
-      </c>
-      <c r="E52" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920109</v>
-      </c>
-      <c r="B53" t="s">
-        <v>91</v>
-      </c>
-      <c r="C53" t="s">
-        <v>101</v>
-      </c>
-      <c r="D53" t="s">
-        <v>145</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920111</v>
-      </c>
-      <c r="B54" t="s">
-        <v>92</v>
-      </c>
-      <c r="C54" t="s">
-        <v>114</v>
-      </c>
-      <c r="D54" t="s">
-        <v>146</v>
-      </c>
-      <c r="E54" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920112</v>
-      </c>
-      <c r="B55" t="s">
-        <v>93</v>
-      </c>
-      <c r="C55" t="s">
-        <v>115</v>
-      </c>
-      <c r="D55" t="s">
-        <v>147</v>
-      </c>
-      <c r="E55" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920113</v>
-      </c>
-      <c r="B56" t="s">
-        <v>94</v>
-      </c>
-      <c r="C56" t="s">
-        <v>116</v>
-      </c>
-      <c r="D56" t="s">
-        <v>148</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920113</v>
-      </c>
-      <c r="B57" t="s">
-        <v>94</v>
-      </c>
-      <c r="C57" t="s">
-        <v>116</v>
-      </c>
-      <c r="D57" t="s">
-        <v>148</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -5265,16 +4548,16 @@
         <v>20330051920055</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5282,16 +4565,16 @@
         <v>20330051920097</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5299,81 +4582,78 @@
         <v>20330051920042</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920366</v>
+        <v>20330051920099</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920367</v>
+        <v>20330051920366</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920100</v>
+        <v>20330051920367</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920039</v>
+        <v>20330051920100</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -5381,19 +4661,19 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920045</v>
+        <v>20330051920039</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5401,16 +4681,16 @@
         <v>20330051920046</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5418,404 +4698,407 @@
         <v>20330051920052</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920056</v>
+        <v>20330051920102</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920096</v>
+        <v>20330051920040</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920099</v>
+        <v>20330051920043</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>94</v>
+      </c>
+      <c r="C14" t="s">
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920102</v>
+        <v>20330051920044</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920113</v>
+        <v>20330051920045</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
         <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920040</v>
+        <v>20330051920048</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920043</v>
+        <v>20330051920050</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920044</v>
+        <v>20330051920051</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920048</v>
+        <v>20330051920365</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920050</v>
+        <v>20330051920053</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920051</v>
+        <v>20330051920056</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920365</v>
+        <v>20330051920057</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920053</v>
+        <v>20330051920095</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920057</v>
+        <v>20330051920096</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920095</v>
+        <v>20330051920101</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920101</v>
+        <v>20330051920058</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920058</v>
+        <v>20330051920104</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920104</v>
+        <v>20330051920105</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920105</v>
+        <v>20330051920107</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920107</v>
+        <v>20330051920109</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920109</v>
+        <v>20330051920111</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920111</v>
+        <v>20330051920112</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920112</v>
+        <v>20330051920113</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D34" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5825,7 +5108,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5857,45 +5140,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920040</v>
+        <v>20330051920044</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920040</v>
+        <v>20330051920044</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5903,45 +5186,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920045</v>
+        <v>20330051920052</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920045</v>
+        <v>20330051920052</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5949,22 +5232,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920046</v>
+        <v>20330051920099</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
       </c>
-      <c r="C6" t="s">
-        <v>101</v>
-      </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5972,22 +5252,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920046</v>
+        <v>20330051920099</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
-      <c r="C7" t="s">
-        <v>101</v>
-      </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -5995,22 +5272,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920365</v>
+        <v>20330051920102</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -6018,22 +5295,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920365</v>
+        <v>20330051920102</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6041,45 +5318,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920052</v>
+        <v>20330051920040</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920052</v>
+        <v>20330051920046</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -6087,131 +5364,137 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920056</v>
+        <v>20330051920365</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
         <v>56</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920056</v>
+        <v>20330051920096</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>54</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920099</v>
+        <v>20330051920101</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>105</v>
+      </c>
+      <c r="C14" t="s">
+        <v>123</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>54</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920099</v>
+        <v>20330051920107</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>108</v>
+      </c>
+      <c r="C15" t="s">
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920101</v>
+        <v>20330051920109</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>54</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920101</v>
+        <v>20330051920112</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -6219,370 +5502,25 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920107</v>
+        <v>20330051920113</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
         <v>54</v>
       </c>
       <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920107</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" t="s">
-        <v>144</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920109</v>
-      </c>
-      <c r="B20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" t="s">
-        <v>145</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920109</v>
-      </c>
-      <c r="B21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>145</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920112</v>
-      </c>
-      <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" t="s">
-        <v>147</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920112</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920043</v>
-      </c>
-      <c r="B24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" t="s">
-        <v>120</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920048</v>
-      </c>
-      <c r="B25" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" t="s">
-        <v>124</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920050</v>
-      </c>
-      <c r="B26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920051</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" t="s">
-        <v>102</v>
-      </c>
-      <c r="D27" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920053</v>
-      </c>
-      <c r="B28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" t="s">
-        <v>128</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920057</v>
-      </c>
-      <c r="B29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" t="s">
-        <v>131</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920095</v>
-      </c>
-      <c r="B30" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" t="s">
-        <v>79</v>
-      </c>
-      <c r="D30" t="s">
-        <v>132</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920058</v>
-      </c>
-      <c r="B31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" t="s">
-        <v>113</v>
-      </c>
-      <c r="D31" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>54</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920104</v>
-      </c>
-      <c r="B32" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" t="s">
-        <v>142</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>54</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>20330051920105</v>
-      </c>
-      <c r="B33" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" t="s">
-        <v>143</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>54</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4BEM - Estadisticos 20212.xlsx
+++ b/grupos/4BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -197,12 +197,12 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -242,205 +242,205 @@
     <t>NUBE</t>
   </si>
   <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>HIRAM FABIAN</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>OLMOS</t>
   </si>
   <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>GARCÍA</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
   </si>
   <si>
     <t>ROBLES</t>
   </si>
   <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>HIRAM FABIAN</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>RAUL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>MARIA ASUNCION</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>NOEL ALBERTO</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
   </si>
   <si>
     <t>IVAN</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>GARCÍA</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>RAUL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>MARIA ASUNCION</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>NOEL ALBERTO</t>
-  </si>
-  <si>
-    <t>LUIS ALBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
   </si>
   <si>
     <t>ZURIEL ARTURO</t>
@@ -2936,7 +2936,7 @@
         <v>6</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -2999,7 +2999,7 @@
         <v>6</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>5</v>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -4031,30 +4031,30 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>87.88</v>
+      </c>
+      <c r="G7">
+        <v>12.12</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>84.84999999999999</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>7.9</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15.15</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
@@ -4066,22 +4066,22 @@
         <v>29</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>87.88</v>
       </c>
       <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>7.9</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8">
         <v>12.12</v>
-      </c>
-      <c r="H8">
-        <v>6</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4091,7 +4091,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4126,10 +4126,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4146,10 +4146,10 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4166,10 +4166,10 @@
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -4186,10 +4186,10 @@
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -4206,10 +4206,10 @@
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4229,7 +4229,7 @@
         <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -4249,7 +4249,7 @@
         <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -4269,13 +4269,13 @@
         <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4286,10 +4286,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -4306,10 +4306,10 @@
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -4326,16 +4326,16 @@
         <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4346,7 +4346,7 @@
         <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -4363,7 +4363,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
@@ -4383,7 +4383,7 @@
         <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -4403,13 +4403,13 @@
         <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4423,7 +4423,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -4443,13 +4443,13 @@
         <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4460,10 +4460,10 @@
         <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -4480,36 +4480,16 @@
         <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
       </c>
       <c r="F20" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920102</v>
-      </c>
-      <c r="B21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" t="s">
-        <v>92</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4554,7 +4534,7 @@
         <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -4568,10 +4548,10 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -4585,10 +4565,10 @@
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -4602,7 +4582,7 @@
         <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -4619,7 +4599,7 @@
         <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4636,7 +4616,7 @@
         <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -4650,10 +4630,10 @@
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -4667,10 +4647,10 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4684,10 +4664,10 @@
         <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4701,10 +4681,10 @@
         <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4712,30 +4692,30 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920102</v>
+        <v>20330051920040</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920040</v>
+        <v>20330051920043</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
         <v>128</v>
@@ -4746,13 +4726,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920043</v>
+        <v>20330051920044</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
         <v>129</v>
@@ -4763,13 +4743,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920044</v>
+        <v>20330051920045</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
         <v>130</v>
@@ -4780,13 +4760,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920045</v>
+        <v>20330051920048</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
         <v>131</v>
@@ -4797,13 +4777,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920048</v>
+        <v>20330051920050</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
         <v>132</v>
@@ -4814,16 +4794,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920050</v>
+        <v>20330051920051</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4831,16 +4811,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920051</v>
+        <v>20330051920365</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4848,13 +4828,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920365</v>
+        <v>20330051920053</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
         <v>134</v>
@@ -4865,13 +4845,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920053</v>
+        <v>20330051920056</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D21" t="s">
         <v>135</v>
@@ -4882,13 +4862,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920056</v>
+        <v>20330051920057</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -4899,13 +4879,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920057</v>
+        <v>20330051920095</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
         <v>137</v>
@@ -4916,13 +4896,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920095</v>
+        <v>20330051920096</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
         <v>138</v>
@@ -4933,13 +4913,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920096</v>
+        <v>20330051920101</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
         <v>139</v>
@@ -4950,13 +4930,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920101</v>
+        <v>20330051920102</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4970,10 +4950,10 @@
         <v>20330051920058</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4987,10 +4967,10 @@
         <v>20330051920104</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -5004,10 +4984,10 @@
         <v>20330051920105</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -5021,10 +5001,10 @@
         <v>20330051920107</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
@@ -5038,10 +5018,10 @@
         <v>20330051920109</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -5055,10 +5035,10 @@
         <v>20330051920111</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -5072,10 +5052,10 @@
         <v>20330051920112</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
         <v>147</v>
@@ -5089,10 +5069,10 @@
         <v>20330051920113</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
         <v>148</v>
@@ -5108,7 +5088,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5143,13 +5123,13 @@
         <v>20330051920044</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5166,13 +5146,13 @@
         <v>20330051920044</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5192,10 +5172,10 @@
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5215,10 +5195,10 @@
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -5238,7 +5218,7 @@
         <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5258,7 +5238,7 @@
         <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -5272,68 +5252,68 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920102</v>
+        <v>20330051920040</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920102</v>
+        <v>20330051920046</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920040</v>
+        <v>20330051920365</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5341,45 +5321,45 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920046</v>
+        <v>20330051920096</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920365</v>
+        <v>20330051920101</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5387,16 +5367,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920096</v>
+        <v>20330051920102</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
         <v>122</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5410,16 +5390,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920101</v>
+        <v>20330051920107</v>
       </c>
       <c r="B14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -5433,16 +5413,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920107</v>
+        <v>20330051920109</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -5456,16 +5436,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920109</v>
+        <v>20330051920112</v>
       </c>
       <c r="B16" t="s">
         <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -5479,16 +5459,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920112</v>
+        <v>20330051920113</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C17" t="s">
         <v>126</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -5497,29 +5477,6 @@
         <v>54</v>
       </c>
       <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920113</v>
-      </c>
-      <c r="B18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" t="s">
-        <v>127</v>
-      </c>
-      <c r="D18" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BEM - Estadisticos 20212.xlsx
+++ b/grupos/4BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -197,10 +197,10 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>NC</t>
@@ -990,16 +990,16 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1038,7 +1038,7 @@
         <v>7</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>10</v>
@@ -1079,16 +1079,16 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1121,7 +1121,7 @@
         <v>6</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>-1</v>
@@ -1130,7 +1130,7 @@
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB5">
         <v>5</v>
@@ -1168,16 +1168,16 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1210,16 +1210,16 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>5</v>
@@ -1263,7 +1263,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1346,16 +1346,16 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>5</v>
@@ -1435,16 +1435,16 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1477,13 +1477,13 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA9">
         <v>6</v>
@@ -1524,16 +1524,16 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1566,7 +1566,7 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1575,7 +1575,7 @@
         <v>10</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB10">
         <v>7</v>
@@ -1613,13 +1613,13 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1655,13 +1655,13 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA11">
         <v>10</v>
@@ -1702,16 +1702,16 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1797,7 +1797,7 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1880,16 +1880,16 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1922,16 +1922,16 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>6</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB14">
         <v>6</v>
@@ -1969,16 +1969,16 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -2011,7 +2011,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -2020,7 +2020,7 @@
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB15">
         <v>6</v>
@@ -2058,16 +2058,16 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2100,16 +2100,16 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB16">
         <v>6</v>
@@ -2147,16 +2147,16 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2189,16 +2189,16 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>6</v>
       </c>
       <c r="Z17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>7</v>
@@ -2236,16 +2236,16 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2278,7 +2278,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -2331,7 +2331,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2414,16 +2414,16 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2456,16 +2456,16 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>9</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB20">
         <v>6</v>
@@ -2503,16 +2503,16 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2545,7 +2545,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2554,7 +2554,7 @@
         <v>10</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>7</v>
@@ -2592,16 +2592,16 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2634,13 +2634,13 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>6</v>
@@ -2681,13 +2681,13 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2729,7 +2729,7 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>-1</v>
@@ -2770,13 +2770,13 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2818,7 +2818,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>-1</v>
@@ -2859,13 +2859,13 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2948,16 +2948,16 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2990,16 +2990,16 @@
         <v>6</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>8</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB26">
         <v>5</v>
@@ -3037,13 +3037,13 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -3079,13 +3079,13 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA27">
         <v>9</v>
@@ -3126,16 +3126,16 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -3215,16 +3215,16 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3266,7 +3266,7 @@
         <v>10</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB29">
         <v>10</v>
@@ -3304,16 +3304,16 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3346,7 +3346,7 @@
         <v>7</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3393,16 +3393,16 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3435,7 +3435,7 @@
         <v>6</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>6</v>
@@ -3488,7 +3488,7 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3571,13 +3571,13 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3613,7 +3613,7 @@
         <v>5</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3660,16 +3660,16 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3711,7 +3711,7 @@
         <v>6</v>
       </c>
       <c r="AA34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB34">
         <v>5</v>
@@ -3749,13 +3749,13 @@
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3791,7 +3791,7 @@
         <v>6</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>9</v>
@@ -3967,19 +3967,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>81.81999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="G5">
-        <v>18.18</v>
+        <v>15.15</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -4031,30 +4031,30 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>84.84999999999999</v>
+      </c>
+      <c r="G7">
+        <v>3.03</v>
+      </c>
+      <c r="H7">
+        <v>7.9</v>
+      </c>
+      <c r="I7">
         <v>4</v>
       </c>
-      <c r="F7">
-        <v>87.88</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>12.12</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
@@ -4066,22 +4066,22 @@
         <v>29</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F8">
         <v>87.88</v>
       </c>
       <c r="G8">
+        <v>12.12</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
         <v>0</v>
       </c>
-      <c r="H8">
-        <v>7.9</v>
-      </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
       <c r="J8">
-        <v>12.12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4275,7 +4275,7 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4335,7 +4335,7 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4409,7 +4409,7 @@
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4449,7 +4449,7 @@
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -5088,7 +5088,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5166,45 +5166,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920052</v>
+        <v>20330051920099</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920052</v>
+        <v>20330051920099</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5212,39 +5206,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920099</v>
+        <v>20330051920040</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920099</v>
+        <v>20330051920046</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -5252,22 +5252,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920040</v>
+        <v>20330051920365</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5275,45 +5275,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920046</v>
+        <v>20330051920096</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920365</v>
+        <v>20330051920101</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5321,16 +5321,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920096</v>
+        <v>20330051920102</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5344,16 +5344,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920101</v>
+        <v>20330051920107</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -5367,16 +5367,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920102</v>
+        <v>20330051920109</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5390,16 +5390,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920107</v>
+        <v>20330051920112</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="D14" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -5413,16 +5413,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920109</v>
+        <v>20330051920113</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -5431,52 +5431,6 @@
         <v>54</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920112</v>
-      </c>
-      <c r="B16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" t="s">
-        <v>147</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920113</v>
-      </c>
-      <c r="B17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" t="s">
-        <v>126</v>
-      </c>
-      <c r="D17" t="s">
-        <v>148</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BEM - Estadisticos 20212.xlsx
+++ b/grupos/4BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -182,27 +182,27 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,226 +215,226 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANASTACIO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>HIRAM FABIAN</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>ANASTACIO</t>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
   </si>
   <si>
     <t>CID</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>MENDIZABAL</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
     <t>NUBE</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>CONCHE</t>
   </si>
   <si>
-    <t>ROMERO</t>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>GARCÍA</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
   </si>
   <si>
     <t>VALENCIA</t>
   </si>
   <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>SEGURA</t>
   </si>
   <si>
-    <t>EVARISTO</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
   </si>
   <si>
     <t>ALEMAN</t>
   </si>
   <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>GUSTAVO</t>
   </si>
   <si>
-    <t>HIRAM FABIAN</t>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>RAUL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
   </si>
   <si>
     <t>JESUS</t>
   </si>
   <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
     <t>CESAR</t>
   </si>
   <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
+    <t>MARIA ASUNCION</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>NOEL ALBERTO</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
   </si>
   <si>
     <t>ALDER ALBERTO</t>
   </si>
   <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
     <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>GARCÍA</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>RAUL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>MARIA ASUNCION</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>NOEL ALBERTO</t>
-  </si>
-  <si>
-    <t>LUIS ALBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
   </si>
   <si>
     <t>SERGIO MARIANO</t>
@@ -993,7 +993,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>6</v>
@@ -1002,10 +1002,10 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1044,10 +1044,10 @@
         <v>10</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1061,7 +1061,7 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -1082,7 +1082,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -1091,10 +1091,10 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1124,7 +1124,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z5">
         <v>5</v>
@@ -1133,10 +1133,10 @@
         <v>8</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1171,7 +1171,7 @@
         <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -1180,10 +1180,10 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1213,7 +1213,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z6">
         <v>8</v>
@@ -1222,10 +1222,10 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1239,7 +1239,7 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1257,10 +1257,10 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1269,7 +1269,7 @@
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1302,7 +1302,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -1311,7 +1311,7 @@
         <v>6</v>
       </c>
       <c r="AB7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>-1</v>
@@ -1349,7 +1349,7 @@
         <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -1358,10 +1358,10 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1391,7 +1391,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z8">
         <v>5</v>
@@ -1400,10 +1400,10 @@
         <v>7</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1417,7 +1417,7 @@
         <v>6</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1438,7 +1438,7 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -1447,10 +1447,10 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1480,7 +1480,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>7</v>
@@ -1489,10 +1489,10 @@
         <v>6</v>
       </c>
       <c r="AB9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1527,7 +1527,7 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1536,10 +1536,10 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1578,10 +1578,10 @@
         <v>9</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1616,7 +1616,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>8</v>
@@ -1625,10 +1625,10 @@
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1667,10 +1667,10 @@
         <v>10</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1705,7 +1705,7 @@
         <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1714,10 +1714,10 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1756,7 +1756,7 @@
         <v>10</v>
       </c>
       <c r="AB12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>9</v>
@@ -1773,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -1791,10 +1791,10 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -1803,7 +1803,7 @@
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1836,7 +1836,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -1845,7 +1845,7 @@
         <v>-1</v>
       </c>
       <c r="AB13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>-1</v>
@@ -1883,7 +1883,7 @@
         <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -1892,10 +1892,10 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1934,7 +1934,7 @@
         <v>9</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>10</v>
@@ -1972,7 +1972,7 @@
         <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>6</v>
@@ -1981,10 +1981,10 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -2014,7 +2014,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <v>5</v>
@@ -2023,10 +2023,10 @@
         <v>7</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2040,7 +2040,7 @@
         <v>5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -2061,7 +2061,7 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -2070,10 +2070,10 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2103,7 +2103,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z16">
         <v>5</v>
@@ -2112,10 +2112,10 @@
         <v>5</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2150,7 +2150,7 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -2159,10 +2159,10 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2201,10 +2201,10 @@
         <v>9</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2239,7 +2239,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -2248,10 +2248,10 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2281,7 +2281,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z18">
         <v>10</v>
@@ -2290,10 +2290,10 @@
         <v>10</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2307,7 +2307,7 @@
         <v>6</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -2325,10 +2325,10 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -2337,7 +2337,7 @@
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2367,10 +2367,10 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z19">
         <v>5</v>
@@ -2417,7 +2417,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -2426,10 +2426,10 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2459,7 +2459,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>7</v>
@@ -2468,7 +2468,7 @@
         <v>8</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2506,7 +2506,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2515,10 +2515,10 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2557,10 +2557,10 @@
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2595,7 +2595,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -2604,10 +2604,10 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2637,7 +2637,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>8</v>
@@ -2646,10 +2646,10 @@
         <v>6</v>
       </c>
       <c r="AB22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2663,7 +2663,7 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E23">
         <v>6</v>
@@ -2684,7 +2684,7 @@
         <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -2693,10 +2693,10 @@
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2726,7 +2726,7 @@
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z23">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>-1</v>
       </c>
       <c r="AB23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -2752,7 +2752,7 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -2773,7 +2773,7 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -2782,10 +2782,10 @@
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2815,7 +2815,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z24">
         <v>7</v>
@@ -2824,7 +2824,7 @@
         <v>-1</v>
       </c>
       <c r="AB24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC24">
         <v>6</v>
@@ -2841,7 +2841,7 @@
         <v>5</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E25">
         <v>5</v>
@@ -2853,7 +2853,7 @@
         <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2862,7 +2862,7 @@
         <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -2871,10 +2871,10 @@
         <v>-1</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2904,7 +2904,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z25">
         <v>5</v>
@@ -2913,10 +2913,10 @@
         <v>6</v>
       </c>
       <c r="AB25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC25">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2951,7 +2951,7 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>7</v>
@@ -2960,10 +2960,10 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -3002,10 +3002,10 @@
         <v>7</v>
       </c>
       <c r="AB26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3040,7 +3040,7 @@
         <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -3049,10 +3049,10 @@
         <v>-1</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3091,10 +3091,10 @@
         <v>9</v>
       </c>
       <c r="AB27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3129,7 +3129,7 @@
         <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>6</v>
@@ -3138,10 +3138,10 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3171,7 +3171,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z28">
         <v>6</v>
@@ -3180,7 +3180,7 @@
         <v>6</v>
       </c>
       <c r="AB28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC28">
         <v>8</v>
@@ -3218,7 +3218,7 @@
         <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -3227,10 +3227,10 @@
         <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3272,7 +3272,7 @@
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3307,7 +3307,7 @@
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -3316,10 +3316,10 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3349,7 +3349,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z30">
         <v>10</v>
@@ -3358,10 +3358,10 @@
         <v>10</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3396,7 +3396,7 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -3405,10 +3405,10 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3438,7 +3438,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z31">
         <v>6</v>
@@ -3447,7 +3447,7 @@
         <v>8</v>
       </c>
       <c r="AB31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>8</v>
@@ -3482,10 +3482,10 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
         <v>6</v>
@@ -3494,10 +3494,10 @@
         <v>-1</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3524,10 +3524,10 @@
         <v>6</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z32">
         <v>6</v>
@@ -3536,10 +3536,10 @@
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3574,7 +3574,7 @@
         <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -3583,10 +3583,10 @@
         <v>-1</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3616,7 +3616,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z33">
         <v>5</v>
@@ -3625,10 +3625,10 @@
         <v>6</v>
       </c>
       <c r="AB33">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3663,7 +3663,7 @@
         <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -3672,10 +3672,10 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3705,7 +3705,7 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z34">
         <v>6</v>
@@ -3714,10 +3714,10 @@
         <v>8</v>
       </c>
       <c r="AB34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC34">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3752,7 +3752,7 @@
         <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>9</v>
@@ -3761,10 +3761,10 @@
         <v>-1</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3803,10 +3803,10 @@
         <v>8</v>
       </c>
       <c r="AB35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC35">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3862,7 +3862,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3871,19 +3871,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>48.48</v>
+        <v>72.73</v>
       </c>
       <c r="G2">
-        <v>51.52</v>
+        <v>27.27</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3903,30 +3903,30 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>72.73</v>
+      </c>
+      <c r="G3">
+        <v>27.27</v>
+      </c>
+      <c r="H3">
+        <v>7.1</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>69.7</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>7.6</v>
-      </c>
-      <c r="I3">
-        <v>10</v>
-      </c>
-      <c r="J3">
-        <v>30.3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3935,19 +3935,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>72.73</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="G4">
-        <v>27.27</v>
+        <v>24.24</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3970,27 +3970,27 @@
         <v>28</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>84.84999999999999</v>
       </c>
       <c r="G5">
-        <v>15.15</v>
+        <v>3.03</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -3999,30 +3999,30 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>87.88</v>
+      </c>
+      <c r="G6">
+        <v>12.12</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>84.84999999999999</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>7.9</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>15.15</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -4031,30 +4031,30 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>84.84999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="G7">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>12.12</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
@@ -4063,19 +4063,19 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>87.88</v>
+        <v>96.97</v>
       </c>
       <c r="G8">
-        <v>12.12</v>
+        <v>3.03</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4091,7 +4091,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4120,376 +4120,142 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920039</v>
+        <v>20330051920042</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920042</v>
+        <v>20330051920055</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920042</v>
+        <v>20330051920055</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920046</v>
+        <v>20330051920097</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920052</v>
+        <v>20330051920097</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920055</v>
+        <v>20330051920366</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920055</v>
+        <v>20330051920367</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920055</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920097</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920097</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920097</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920099</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920099</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920366</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920366</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920367</v>
-      </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920367</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920100</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920100</v>
-      </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" t="s">
-        <v>89</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4528,16 +4294,16 @@
         <v>20330051920055</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4545,16 +4311,16 @@
         <v>20330051920097</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4562,143 +4328,146 @@
         <v>20330051920042</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920099</v>
+        <v>20330051920366</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920366</v>
+        <v>20330051920367</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920367</v>
+        <v>20330051920039</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920100</v>
+        <v>20330051920040</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920039</v>
+        <v>20330051920043</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920046</v>
+        <v>20330051920044</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920052</v>
+        <v>20330051920045</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920040</v>
+        <v>20330051920046</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
         <v>127</v>
@@ -4709,13 +4478,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920043</v>
+        <v>20330051920048</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
         <v>128</v>
@@ -4726,13 +4495,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920044</v>
+        <v>20330051920050</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
         <v>129</v>
@@ -4743,16 +4512,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920045</v>
+        <v>20330051920051</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4760,16 +4529,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920048</v>
+        <v>20330051920365</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4777,16 +4546,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920050</v>
+        <v>20330051920052</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4794,16 +4563,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920051</v>
+        <v>20330051920053</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4811,13 +4580,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920365</v>
+        <v>20330051920056</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4828,13 +4597,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920053</v>
+        <v>20330051920057</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
         <v>134</v>
@@ -4845,13 +4614,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920056</v>
+        <v>20330051920095</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
         <v>135</v>
@@ -4862,13 +4631,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920057</v>
+        <v>20330051920096</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -4879,13 +4648,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920095</v>
+        <v>20330051920099</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C23" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
         <v>137</v>
@@ -4896,13 +4662,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920096</v>
+        <v>20330051920100</v>
       </c>
       <c r="B24" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
         <v>138</v>
@@ -4916,10 +4682,10 @@
         <v>20330051920101</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
         <v>139</v>
@@ -4933,10 +4699,10 @@
         <v>20330051920102</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4950,10 +4716,10 @@
         <v>20330051920058</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4967,10 +4733,10 @@
         <v>20330051920104</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4984,10 +4750,10 @@
         <v>20330051920105</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -5001,10 +4767,10 @@
         <v>20330051920107</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
@@ -5018,10 +4784,10 @@
         <v>20330051920109</v>
       </c>
       <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" t="s">
         <v>107</v>
-      </c>
-      <c r="C31" t="s">
-        <v>76</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -5035,10 +4801,10 @@
         <v>20330051920111</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -5052,10 +4818,10 @@
         <v>20330051920112</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
         <v>147</v>
@@ -5069,10 +4835,10 @@
         <v>20330051920113</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
         <v>148</v>
@@ -5088,7 +4854,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5120,22 +4886,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920044</v>
+        <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5143,22 +4909,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920044</v>
+        <v>20330051920039</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5169,19 +4935,19 @@
         <v>20330051920099</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5189,39 +4955,39 @@
         <v>20330051920099</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920040</v>
+        <v>20330051920111</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5229,45 +4995,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920046</v>
+        <v>20330051920111</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>55</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920365</v>
+        <v>20330051920044</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5275,22 +5041,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920096</v>
+        <v>20330051920365</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5298,139 +5064,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920101</v>
+        <v>20330051920109</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920102</v>
-      </c>
-      <c r="B11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D11" t="s">
-        <v>140</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920107</v>
-      </c>
-      <c r="B12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920109</v>
-      </c>
-      <c r="B13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920112</v>
-      </c>
-      <c r="B14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D14" t="s">
-        <v>147</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920113</v>
-      </c>
-      <c r="B15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" t="s">
-        <v>126</v>
-      </c>
-      <c r="D15" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BEM - Estadisticos 20212.xlsx
+++ b/grupos/4BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -182,6 +182,9 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
@@ -192,9 +195,6 @@
   </si>
   <si>
     <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
   </si>
   <si>
     <t>Jiménez Nieto Enrique</t>
@@ -987,7 +987,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -1076,7 +1076,7 @@
         <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>7</v>
@@ -1118,7 +1118,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1165,7 +1165,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -1254,7 +1254,7 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1296,7 +1296,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1343,7 +1343,7 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>7</v>
@@ -1432,7 +1432,7 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>7</v>
@@ -1474,7 +1474,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1521,7 +1521,7 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>9</v>
@@ -1610,7 +1610,7 @@
         <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>9</v>
@@ -1699,7 +1699,7 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>9</v>
@@ -1788,7 +1788,7 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1877,7 +1877,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>9</v>
@@ -1966,7 +1966,7 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>8</v>
@@ -2055,7 +2055,7 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>8</v>
@@ -2144,7 +2144,7 @@
         <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>9</v>
@@ -2233,7 +2233,7 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -2322,7 +2322,7 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -2411,7 +2411,7 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>9</v>
@@ -2500,7 +2500,7 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>9</v>
@@ -2589,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>9</v>
@@ -2678,7 +2678,7 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>5</v>
@@ -2720,7 +2720,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2767,7 +2767,7 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>5</v>
@@ -2809,7 +2809,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2856,7 +2856,7 @@
         <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>5</v>
@@ -2945,7 +2945,7 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>9</v>
@@ -2987,7 +2987,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -3034,7 +3034,7 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -3076,7 +3076,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -3123,7 +3123,7 @@
         <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>7</v>
@@ -3212,7 +3212,7 @@
         <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -3301,7 +3301,7 @@
         <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>9</v>
@@ -3390,7 +3390,7 @@
         <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>9</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3479,7 +3479,7 @@
         <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>5</v>
@@ -3521,7 +3521,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -3568,7 +3568,7 @@
         <v>7</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>7</v>
@@ -3657,7 +3657,7 @@
         <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>7</v>
@@ -3746,7 +3746,7 @@
         <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>9</v>
@@ -3862,7 +3862,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3871,19 +3871,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>72.73</v>
+        <v>63.64</v>
       </c>
       <c r="G2">
-        <v>27.27</v>
+        <v>36.36</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3915,7 +3915,7 @@
         <v>27.27</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3926,7 +3926,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3935,19 +3935,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>75.76000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="G4">
-        <v>24.24</v>
+        <v>27.27</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3967,30 +3967,30 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>84.84999999999999</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="G5">
-        <v>3.03</v>
+        <v>24.24</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>12.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -3999,25 +3999,25 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>84.84999999999999</v>
+      </c>
+      <c r="G6">
+        <v>3.03</v>
+      </c>
+      <c r="H6">
+        <v>7.9</v>
+      </c>
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="F6">
-        <v>87.88</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>12.12</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4175,7 +4175,7 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4215,7 +4215,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4235,7 +4235,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4255,7 +4255,7 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4854,7 +4854,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4886,22 +4886,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920039</v>
+        <v>20330051920099</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4909,19 +4906,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920039</v>
+        <v>20330051920099</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>55</v>
@@ -4932,19 +4926,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920099</v>
+        <v>20330051920109</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4952,19 +4949,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920099</v>
+        <v>20330051920109</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>98</v>
+      </c>
+      <c r="C5" t="s">
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4987,7 +4987,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5010,7 +5010,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5033,7 +5033,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5041,22 +5041,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920365</v>
+        <v>20330051920046</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5064,24 +5064,70 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920109</v>
+        <v>20330051920365</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>56</v>
       </c>
       <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920101</v>
+      </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920107</v>
+      </c>
+      <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BEM - Estadisticos 20212.xlsx
+++ b/grupos/4BEM - Estadisticos 20212.xlsx
@@ -1622,7 +1622,7 @@
         <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>10</v>
@@ -1664,7 +1664,7 @@
         <v>9</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB11">
         <v>9</v>

--- a/grupos/4BEM - Estadisticos 20212.xlsx
+++ b/grupos/4BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -185,21 +185,21 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
@@ -224,214 +224,214 @@
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>HIRAM FABIAN</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>HIRAM FABIAN</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>GARCÍA</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>RAUL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>MARIA ASUNCION</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>NOEL ALBERTO</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
   </si>
   <si>
     <t>ELI ANTONIO</t>
   </si>
   <si>
     <t>ISAAC</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>GARCÍA</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>RAUL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>MARIA ASUNCION</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>NOEL ALBERTO</t>
-  </si>
-  <si>
-    <t>LUIS ALBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
   </si>
   <si>
     <t>CHRISTIAN YAIR</t>
@@ -1011,16 +1011,16 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -1038,7 +1038,7 @@
         <v>7</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4">
         <v>10</v>
@@ -1100,16 +1100,16 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1121,13 +1121,13 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>8</v>
@@ -1189,16 +1189,16 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1213,10 +1213,10 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -1266,7 +1266,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>9</v>
@@ -1278,13 +1278,13 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1302,13 +1302,13 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -1367,16 +1367,16 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1388,16 +1388,16 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -1456,16 +1456,16 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1483,10 +1483,10 @@
         <v>6</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB9">
         <v>8</v>
@@ -1539,22 +1539,22 @@
         <v>9</v>
       </c>
       <c r="O10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1572,7 +1572,7 @@
         <v>9</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA10">
         <v>9</v>
@@ -1581,7 +1581,7 @@
         <v>8</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1634,16 +1634,16 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1658,10 +1658,10 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -1723,16 +1723,16 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1747,7 +1747,7 @@
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>10</v>
@@ -1779,7 +1779,7 @@
         <v>5</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1800,7 +1800,7 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>9</v>
@@ -1812,16 +1812,16 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1836,13 +1836,13 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>7</v>
@@ -1901,16 +1901,16 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1925,7 +1925,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>6</v>
@@ -1990,16 +1990,16 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -2011,16 +2011,16 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>8</v>
@@ -2079,16 +2079,16 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -2103,13 +2103,13 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB16">
         <v>8</v>
@@ -2168,16 +2168,16 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2189,13 +2189,13 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -2251,22 +2251,22 @@
         <v>10</v>
       </c>
       <c r="O18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2293,7 +2293,7 @@
         <v>9</v>
       </c>
       <c r="AC18">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2313,7 +2313,7 @@
         <v>5</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2346,13 +2346,13 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2376,7 +2376,7 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB19">
         <v>5</v>
@@ -2435,16 +2435,16 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2456,13 +2456,13 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>7</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA20">
         <v>8</v>
@@ -2524,16 +2524,16 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2551,7 +2551,7 @@
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -2613,16 +2613,16 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2643,7 +2643,7 @@
         <v>8</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB22">
         <v>8</v>
@@ -2669,7 +2669,7 @@
         <v>6</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2702,13 +2702,13 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -2729,10 +2729,10 @@
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB23">
         <v>7</v>
@@ -2758,7 +2758,7 @@
         <v>5</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -2791,13 +2791,13 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -2818,10 +2818,10 @@
         <v>5</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB24">
         <v>7</v>
@@ -2880,13 +2880,13 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -2969,16 +2969,16 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2996,7 +2996,7 @@
         <v>8</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA26">
         <v>7</v>
@@ -3046,7 +3046,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>9</v>
@@ -3058,16 +3058,16 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -3085,10 +3085,10 @@
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>7</v>
@@ -3147,16 +3147,16 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -3168,13 +3168,13 @@
         <v>6</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA28">
         <v>6</v>
@@ -3236,16 +3236,16 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3263,7 +3263,7 @@
         <v>8</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA29">
         <v>9</v>
@@ -3325,16 +3325,16 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3346,7 +3346,7 @@
         <v>7</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -3414,16 +3414,16 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3435,16 +3435,16 @@
         <v>5</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>7</v>
       </c>
       <c r="Z31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB31">
         <v>8</v>
@@ -3503,13 +3503,13 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
         <v>-1</v>
@@ -3527,7 +3527,7 @@
         <v>5</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z32">
         <v>6</v>
@@ -3571,7 +3571,7 @@
         <v>5</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>5</v>
@@ -3580,7 +3580,7 @@
         <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>10</v>
@@ -3592,13 +3592,13 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
         <v>-1</v>
@@ -3619,7 +3619,7 @@
         <v>6</v>
       </c>
       <c r="Z33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA33">
         <v>6</v>
@@ -3681,16 +3681,16 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3705,13 +3705,13 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z34">
         <v>6</v>
       </c>
       <c r="AA34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB34">
         <v>7</v>
@@ -3758,7 +3758,7 @@
         <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N35">
         <v>9</v>
@@ -3770,16 +3770,16 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3794,10 +3794,10 @@
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA35">
         <v>8</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3903,19 +3903,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>72.73</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="G3">
-        <v>27.27</v>
+        <v>21.21</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3926,7 +3926,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3935,19 +3935,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>72.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="G4">
-        <v>27.27</v>
+        <v>15.15</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3967,25 +3967,25 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>75.76000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="G5">
-        <v>24.24</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3999,30 +3999,30 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>84.84999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="G6">
-        <v>3.03</v>
+        <v>9.09</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>12.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -4031,25 +4031,25 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>93.94</v>
+      </c>
+      <c r="G7">
+        <v>6.06</v>
+      </c>
+      <c r="H7">
+        <v>7.2</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>90.91</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>8.1</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>9.09</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -4091,7 +4091,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4126,16 +4126,16 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4146,24 +4146,24 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920055</v>
+        <v>20330051920097</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
         <v>70</v>
@@ -4172,90 +4172,10 @@
         <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920097</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920097</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920366</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920367</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4291,50 +4211,50 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920055</v>
+        <v>20330051920042</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920097</v>
+        <v>20330051920055</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920042</v>
+        <v>20330051920097</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -4342,44 +4262,44 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920366</v>
+        <v>20330051920039</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920367</v>
+        <v>20330051920040</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920039</v>
+        <v>20330051920043</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
         <v>102</v>
@@ -4393,10 +4313,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920040</v>
+        <v>20330051920044</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
         <v>103</v>
@@ -4410,10 +4330,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920043</v>
+        <v>20330051920045</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
@@ -4427,10 +4347,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920044</v>
+        <v>20330051920046</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
         <v>105</v>
@@ -4444,13 +4364,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920045</v>
+        <v>20330051920048</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
         <v>126</v>
@@ -4461,13 +4381,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920046</v>
+        <v>20330051920050</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
         <v>127</v>
@@ -4478,16 +4398,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920048</v>
+        <v>20330051920051</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4495,16 +4415,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920050</v>
+        <v>20330051920365</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4512,16 +4432,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920051</v>
+        <v>20330051920052</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
         <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4529,10 +4449,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920365</v>
+        <v>20330051920053</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
         <v>109</v>
@@ -4546,10 +4466,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920052</v>
+        <v>20330051920056</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
         <v>110</v>
@@ -4563,10 +4483,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920053</v>
+        <v>20330051920057</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
         <v>111</v>
@@ -4580,13 +4500,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920056</v>
+        <v>20330051920095</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4597,13 +4517,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920057</v>
+        <v>20330051920096</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
         <v>134</v>
@@ -4614,12 +4534,9 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920095</v>
+        <v>20330051920099</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" t="s">
         <v>88</v>
       </c>
       <c r="D21" t="s">
@@ -4631,13 +4548,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920096</v>
+        <v>20330051920366</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -4648,10 +4565,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920099</v>
+        <v>20330051920367</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>89</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
       </c>
       <c r="D23" t="s">
         <v>137</v>
@@ -4665,10 +4585,10 @@
         <v>20330051920100</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
         <v>138</v>
@@ -4682,10 +4602,10 @@
         <v>20330051920101</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
         <v>139</v>
@@ -4699,10 +4619,10 @@
         <v>20330051920102</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4716,10 +4636,10 @@
         <v>20330051920058</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4733,10 +4653,10 @@
         <v>20330051920104</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4750,10 +4670,10 @@
         <v>20330051920105</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -4767,10 +4687,10 @@
         <v>20330051920107</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
@@ -4784,10 +4704,10 @@
         <v>20330051920109</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -4801,10 +4721,10 @@
         <v>20330051920111</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -4818,10 +4738,10 @@
         <v>20330051920112</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D33" t="s">
         <v>147</v>
@@ -4835,10 +4755,10 @@
         <v>20330051920113</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
         <v>148</v>
@@ -4854,7 +4774,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4886,19 +4806,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920099</v>
+        <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4906,19 +4829,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920099</v>
+        <v>20330051920046</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>79</v>
+      </c>
+      <c r="C3" t="s">
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4926,16 +4852,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920109</v>
+        <v>20330051920101</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4949,22 +4875,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920109</v>
+        <v>20330051920107</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4975,10 +4901,10 @@
         <v>20330051920111</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
         <v>146</v>
@@ -4990,144 +4916,6 @@
         <v>54</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920111</v>
-      </c>
-      <c r="B7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920044</v>
-      </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920046</v>
-      </c>
-      <c r="B9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920365</v>
-      </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" t="s">
-        <v>130</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920101</v>
-      </c>
-      <c r="B11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920107</v>
-      </c>
-      <c r="B12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BEM - Estadisticos 20212.xlsx
+++ b/grupos/4BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -191,18 +191,18 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Torres Sánchez José Luis</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Torres Sánchez José Luis</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,214 +215,214 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
     <t>ANASTACIO</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>GARCÍA</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
   </si>
   <si>
     <t>EVARISTO</t>
   </si>
   <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
     <t>HIRAM FABIAN</t>
   </si>
   <si>
+    <t>RAUL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>MARIA ASUNCION</t>
+  </si>
+  <si>
     <t>MARCO ANTONIO</t>
   </si>
   <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>NOEL ALBERTO</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
     <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>GARCÍA</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>RAUL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>MARIA ASUNCION</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>NOEL ALBERTO</t>
-  </si>
-  <si>
-    <t>LUIS ALBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
   </si>
   <si>
     <t>ALDER ALBERTO</t>
@@ -1008,7 +1008,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>9</v>
@@ -1023,13 +1023,13 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1097,7 +1097,7 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -1112,13 +1112,13 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -1133,7 +1133,7 @@
         <v>8</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>9</v>
@@ -1186,7 +1186,7 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -1201,10 +1201,10 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1251,7 +1251,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>5</v>
@@ -1272,10 +1272,10 @@
         <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -1287,13 +1287,13 @@
         <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1314,7 +1314,7 @@
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1364,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1379,10 +1379,10 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -1453,7 +1453,7 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>9</v>
@@ -1468,13 +1468,13 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1492,7 +1492,7 @@
         <v>8</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1542,7 +1542,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>9</v>
@@ -1557,10 +1557,10 @@
         <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>6</v>
@@ -1631,7 +1631,7 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -1646,10 +1646,10 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -1720,7 +1720,7 @@
         <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1735,10 +1735,10 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1785,7 +1785,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>5</v>
@@ -1806,10 +1806,10 @@
         <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>5</v>
@@ -1824,13 +1824,13 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -1845,10 +1845,10 @@
         <v>7</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1898,7 +1898,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>9</v>
@@ -1913,10 +1913,10 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1987,7 +1987,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>9</v>
@@ -2002,10 +2002,10 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -2076,7 +2076,7 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -2091,10 +2091,10 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -2115,7 +2115,7 @@
         <v>8</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -2180,10 +2180,10 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -2254,7 +2254,7 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -2269,10 +2269,10 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2319,7 +2319,7 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>5</v>
@@ -2334,16 +2334,16 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>5</v>
@@ -2355,13 +2355,13 @@
         <v>5</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2382,7 +2382,7 @@
         <v>5</v>
       </c>
       <c r="AC19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2432,7 +2432,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2447,10 +2447,10 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2471,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2521,7 +2521,7 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>9</v>
@@ -2536,13 +2536,13 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2557,7 +2557,7 @@
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>8</v>
@@ -2610,7 +2610,7 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -2625,10 +2625,10 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2649,7 +2649,7 @@
         <v>8</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2690,7 +2690,7 @@
         <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>9</v>
@@ -2699,7 +2699,7 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -2711,13 +2711,13 @@
         <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2732,13 +2732,13 @@
         <v>7</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2779,7 +2779,7 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>9</v>
@@ -2788,7 +2788,7 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -2800,13 +2800,13 @@
         <v>5</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2824,7 +2824,7 @@
         <v>5</v>
       </c>
       <c r="AB24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC24">
         <v>6</v>
@@ -2868,7 +2868,7 @@
         <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>9</v>
@@ -2877,7 +2877,7 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>5</v>
@@ -2889,13 +2889,13 @@
         <v>5</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2910,7 +2910,7 @@
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB25">
         <v>7</v>
@@ -2966,7 +2966,7 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>9</v>
@@ -2981,13 +2981,13 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -3002,7 +3002,7 @@
         <v>7</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC26">
         <v>8</v>
@@ -3055,7 +3055,7 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>7</v>
@@ -3070,10 +3070,10 @@
         <v>6</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -3094,7 +3094,7 @@
         <v>7</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3144,7 +3144,7 @@
         <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>7</v>
@@ -3159,10 +3159,10 @@
         <v>6</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>6</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>9</v>
@@ -3248,10 +3248,10 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -3269,7 +3269,7 @@
         <v>9</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC29">
         <v>9</v>
@@ -3322,7 +3322,7 @@
         <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -3337,13 +3337,13 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -3358,7 +3358,7 @@
         <v>10</v>
       </c>
       <c r="AB30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -3426,10 +3426,10 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>5</v>
@@ -3450,7 +3450,7 @@
         <v>8</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3491,7 +3491,7 @@
         <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>9</v>
@@ -3500,7 +3500,7 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
         <v>5</v>
@@ -3512,13 +3512,13 @@
         <v>6</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>5</v>
@@ -3533,13 +3533,13 @@
         <v>6</v>
       </c>
       <c r="AA32">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB32">
         <v>7</v>
       </c>
       <c r="AC32">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3589,7 +3589,7 @@
         <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
         <v>8</v>
@@ -3601,13 +3601,13 @@
         <v>8</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>5</v>
@@ -3678,7 +3678,7 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -3693,10 +3693,10 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>6</v>
@@ -3767,7 +3767,7 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
         <v>9</v>
@@ -3782,10 +3782,10 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W35">
         <v>6</v>
@@ -3806,7 +3806,7 @@
         <v>7</v>
       </c>
       <c r="AC35">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3871,16 +3871,16 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>63.64</v>
+        <v>72.73</v>
       </c>
       <c r="G2">
-        <v>36.36</v>
+        <v>27.27</v>
       </c>
       <c r="H2">
         <v>5.8</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3967,30 +3967,30 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>90.91</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>15.15</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
@@ -4075,7 +4075,7 @@
         <v>3.03</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4091,7 +4091,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4116,66 +4116,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920042</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920055</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920097</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4211,64 +4151,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920042</v>
+        <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920055</v>
+        <v>20330051920040</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920097</v>
+        <v>20330051920042</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920039</v>
+        <v>20330051920043</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
         <v>120</v>
@@ -4279,13 +4219,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920040</v>
+        <v>20330051920044</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
         <v>121</v>
@@ -4296,13 +4236,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920043</v>
+        <v>20330051920045</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
         <v>122</v>
@@ -4313,13 +4253,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920044</v>
+        <v>20330051920046</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
         <v>123</v>
@@ -4330,13 +4270,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920045</v>
+        <v>20330051920048</v>
       </c>
       <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
         <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>104</v>
       </c>
       <c r="D9" t="s">
         <v>124</v>
@@ -4347,13 +4287,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920046</v>
+        <v>20330051920050</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
         <v>125</v>
@@ -4364,16 +4304,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920048</v>
+        <v>20330051920051</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4381,16 +4321,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920050</v>
+        <v>20330051920365</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4398,16 +4338,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920051</v>
+        <v>20330051920052</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4415,13 +4355,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920365</v>
+        <v>20330051920053</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
         <v>128</v>
@@ -4432,13 +4372,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920052</v>
+        <v>20330051920055</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
         <v>129</v>
@@ -4449,13 +4389,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920053</v>
+        <v>20330051920056</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
         <v>130</v>
@@ -4466,13 +4406,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920056</v>
+        <v>20330051920057</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
         <v>131</v>
@@ -4483,13 +4423,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920057</v>
+        <v>20330051920095</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
         <v>132</v>
@@ -4500,13 +4440,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920095</v>
+        <v>20330051920096</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4517,13 +4457,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920096</v>
+        <v>20330051920097</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
         <v>134</v>
@@ -4537,7 +4477,7 @@
         <v>20330051920099</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
         <v>135</v>
@@ -4551,10 +4491,10 @@
         <v>20330051920366</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -4568,10 +4508,10 @@
         <v>20330051920367</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
         <v>137</v>
@@ -4585,10 +4525,10 @@
         <v>20330051920100</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
         <v>138</v>
@@ -4602,10 +4542,10 @@
         <v>20330051920101</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
         <v>139</v>
@@ -4619,10 +4559,10 @@
         <v>20330051920102</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4636,10 +4576,10 @@
         <v>20330051920058</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4653,10 +4593,10 @@
         <v>20330051920104</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4670,10 +4610,10 @@
         <v>20330051920105</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -4687,10 +4627,10 @@
         <v>20330051920107</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
@@ -4704,10 +4644,10 @@
         <v>20330051920109</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -4721,10 +4661,10 @@
         <v>20330051920111</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -4738,10 +4678,10 @@
         <v>20330051920112</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
         <v>147</v>
@@ -4755,10 +4695,10 @@
         <v>20330051920113</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
         <v>148</v>
@@ -4774,7 +4714,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4806,22 +4746,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920039</v>
+        <v>20330051920097</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4829,16 +4769,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920046</v>
+        <v>20330051920101</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -4852,16 +4792,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920101</v>
+        <v>20330051920107</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4875,16 +4815,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920107</v>
+        <v>20330051920111</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -4893,29 +4833,6 @@
         <v>54</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920111</v>
-      </c>
-      <c r="B6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
     </row>
